--- a/data/missing_meta/missing_meta.xlsx
+++ b/data/missing_meta/missing_meta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marco_schuppisser/Desktop/Repository sabseb (new)/metasabseb/data/missing_meta/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C87EBACC-0C85-0444-BC69-5ED783758A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F05E10-1A20-6549-AE13-36597237F4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="68640" yWindow="-3840" windowWidth="38400" windowHeight="23500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="68640" yWindow="-3860" windowWidth="38400" windowHeight="23500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="datasets" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7671" uniqueCount="2640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8212" uniqueCount="2662">
   <si>
     <t>var_defs_key</t>
   </si>
@@ -8396,9 +8396,6 @@
     <t>filter_movetia = 1, school_type_id = 3, 8, 9</t>
   </si>
   <si>
-    <t>school_type_id = 1, 2, 3, 4, 5</t>
-  </si>
-  <si>
     <t>school_type_id = 4</t>
   </si>
   <si>
@@ -8408,9 +8405,6 @@
     <t>school_type_id = 8, 9</t>
   </si>
   <si>
-    <t>school_type_id = 1, 3, 4, 5, 8, 9</t>
-  </si>
-  <si>
     <t>school_type_id = 8</t>
   </si>
   <si>
@@ -8436,9 +8430,6 @@
   </si>
   <si>
     <t>Abbruch = 1</t>
-  </si>
-  <si>
-    <t>school_type_id = 1,</t>
   </si>
   <si>
     <t xml:space="preserve">Diese Variable gibt es nicht mehr, Enddatum folgt; Nicht in der Skalendokumentation; ADD INFORMATION: The variable *Untersprach* from sab is only in the raw data and not recorded in the metadata. Please add the information. 
@@ -8458,6 +8449,81 @@
   </si>
   <si>
     <t>school_type_id = 1, 3, 4, 5, 8</t>
+  </si>
+  <si>
+    <t>Skala: Selbstaktivität</t>
+  </si>
+  <si>
+    <t>Einzelitem-Gruppe: Art des Austausches / der Mobilität</t>
+  </si>
+  <si>
+    <t>Skala: Interaktion zwischen Lehrpersonen und Lernenden</t>
+  </si>
+  <si>
+    <t>Skala: Interaktion zwischen Schülerinnen und Schülern</t>
+  </si>
+  <si>
+    <t>Skala: Individuelle Förderung</t>
+  </si>
+  <si>
+    <t>Einzelitem-Gruppe: Selbsteinschätzung der IT-Kompetenzen</t>
+  </si>
+  <si>
+    <t>Skala: Klarheit und Struktur</t>
+  </si>
+  <si>
+    <t>Skala: Selbsteinschätzung der methodischen Kompetenzen</t>
+  </si>
+  <si>
+    <t>Skala: Motivation durch die Lehrperson</t>
+  </si>
+  <si>
+    <t>Einzelitem-Gruppe: Organisation des Austausches / der Mobilität</t>
+  </si>
+  <si>
+    <t>Skala: Selbsteinschätzung der personalen Kompetenzen</t>
+  </si>
+  <si>
+    <t>Skala: Selbstkontrolle und Arbeitsreflexion</t>
+  </si>
+  <si>
+    <t>Skala: Selbsteinschätzung der sozialen Kompetenzen</t>
+  </si>
+  <si>
+    <t>Skala: Störungen im Unterricht</t>
+  </si>
+  <si>
+    <t>Skala: Selbstwirksamkeitserwartung</t>
+  </si>
+  <si>
+    <t>Einzelitem: Über-/Unterforderung</t>
+  </si>
+  <si>
+    <t>Einzelitem-Gruppe: Ort des Austausches / der Mobilität</t>
+  </si>
+  <si>
+    <t>Einzelitem: Zeitliche Belastung</t>
+  </si>
+  <si>
+    <t>Einzelitem: Teilnahme an Austausch und Mobilität</t>
+  </si>
+  <si>
+    <t>Individuelle Eingangsvoraussetzungen der Schülerinnen und Schüler</t>
+  </si>
+  <si>
+    <t>Fragen zu Austausch und Mobilität (Movetia)</t>
+  </si>
+  <si>
+    <t>school_type_id = 1, 4,5: Mean, Ausschluss wenn Missings &gt;1 &amp; school_type_id = 3, 8: Mean, Auschluss wenn Missings &gt; 2</t>
+  </si>
+  <si>
+    <t>school_type_id = 1,3, 4, 5</t>
+  </si>
+  <si>
+    <t>school_type_id = 1, 3, 4, 8</t>
+  </si>
+  <si>
+    <t>Einzelitem: Unterrichtssprache</t>
   </si>
 </sst>
 </file>
@@ -8583,7 +8649,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -8604,7 +8670,6 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
@@ -8612,7 +8677,187 @@
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="2" xr:uid="{BC66F5EB-00B7-4041-B960-07C65FD467B2}"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="44">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -9409,7 +9654,7 @@
         <v>1390</v>
       </c>
       <c r="I2" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="K2" s="8" t="s">
         <v>2547</v>
@@ -9444,7 +9689,7 @@
         <v>1390</v>
       </c>
       <c r="I3" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>2547</v>
@@ -9479,7 +9724,7 @@
         <v>1390</v>
       </c>
       <c r="I4" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="K4" s="8" t="s">
         <v>2547</v>
@@ -9514,7 +9759,7 @@
         <v>1390</v>
       </c>
       <c r="I5" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="K5" s="8" t="s">
         <v>2547</v>
@@ -9549,7 +9794,7 @@
         <v>1390</v>
       </c>
       <c r="I6" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>2547</v>
@@ -9584,7 +9829,7 @@
         <v>1390</v>
       </c>
       <c r="I7" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="K7" s="8" t="s">
         <v>2547</v>
@@ -9619,7 +9864,7 @@
         <v>1390</v>
       </c>
       <c r="I8" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="K8" s="8" t="s">
         <v>2547</v>
@@ -9654,7 +9899,7 @@
         <v>1390</v>
       </c>
       <c r="I9" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="K9" s="8" t="s">
         <v>2547</v>
@@ -9689,7 +9934,7 @@
         <v>1390</v>
       </c>
       <c r="I10" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="K10" s="8" t="s">
         <v>2547</v>
@@ -9724,7 +9969,7 @@
         <v>1390</v>
       </c>
       <c r="I11" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="K11" s="8" t="s">
         <v>2547</v>
@@ -9759,7 +10004,7 @@
         <v>1390</v>
       </c>
       <c r="I12" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="K12" s="8" t="s">
         <v>2547</v>
@@ -9794,7 +10039,7 @@
         <v>1390</v>
       </c>
       <c r="I13" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="K13" s="8" t="s">
         <v>2547</v>
@@ -9846,13 +10091,16 @@
         <v>1350</v>
       </c>
       <c r="D15" t="s">
-        <v>2638</v>
+        <v>2635</v>
       </c>
       <c r="E15" t="s">
         <v>60</v>
       </c>
+      <c r="G15" t="s">
+        <v>1402</v>
+      </c>
       <c r="I15" t="s">
-        <v>2639</v>
+        <v>2636</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>1717</v>
@@ -9881,7 +10129,7 @@
         <v>1390</v>
       </c>
       <c r="I16" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="K16" s="8" t="s">
         <v>2548</v>
@@ -9916,7 +10164,7 @@
         <v>1390</v>
       </c>
       <c r="I17" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="K17" s="8" t="s">
         <v>2548</v>
@@ -9951,7 +10199,7 @@
         <v>1390</v>
       </c>
       <c r="I18" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="K18" s="8" t="s">
         <v>2548</v>
@@ -9986,7 +10234,7 @@
         <v>1390</v>
       </c>
       <c r="I19" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="K19" s="8" t="s">
         <v>2548</v>
@@ -10021,7 +10269,7 @@
         <v>1390</v>
       </c>
       <c r="I20" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="K20" s="8" t="s">
         <v>2548</v>
@@ -10056,7 +10304,7 @@
         <v>1390</v>
       </c>
       <c r="I21" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="K21" s="8" t="s">
         <v>2548</v>
@@ -10091,7 +10339,7 @@
         <v>1390</v>
       </c>
       <c r="I22" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="K22" s="8" t="s">
         <v>2548</v>
@@ -10126,7 +10374,7 @@
         <v>1390</v>
       </c>
       <c r="I23" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="K23" s="8" t="s">
         <v>2548</v>
@@ -10628,12 +10876,21 @@
       <c r="C39" t="s">
         <v>1676</v>
       </c>
+      <c r="D39" t="s">
+        <v>2637</v>
+      </c>
       <c r="E39" t="s">
         <v>85</v>
       </c>
       <c r="F39" t="s">
         <v>86</v>
       </c>
+      <c r="G39" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H39" t="s">
+        <v>1389</v>
+      </c>
       <c r="I39" t="s">
         <v>2612</v>
       </c>
@@ -10657,12 +10914,21 @@
       <c r="C40" t="s">
         <v>1676</v>
       </c>
+      <c r="D40" t="s">
+        <v>2637</v>
+      </c>
       <c r="E40" t="s">
         <v>85</v>
       </c>
       <c r="F40" t="s">
         <v>88</v>
       </c>
+      <c r="G40" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H40" t="s">
+        <v>1389</v>
+      </c>
       <c r="I40" t="s">
         <v>2612</v>
       </c>
@@ -10686,12 +10952,21 @@
       <c r="C41" t="s">
         <v>1676</v>
       </c>
+      <c r="D41" t="s">
+        <v>2637</v>
+      </c>
       <c r="E41" t="s">
         <v>85</v>
       </c>
       <c r="F41" t="s">
         <v>90</v>
       </c>
+      <c r="G41" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H41" t="s">
+        <v>1389</v>
+      </c>
       <c r="I41" t="s">
         <v>2612</v>
       </c>
@@ -10715,12 +10990,21 @@
       <c r="C42" t="s">
         <v>1676</v>
       </c>
+      <c r="D42" t="s">
+        <v>2637</v>
+      </c>
       <c r="E42" t="s">
         <v>85</v>
       </c>
       <c r="F42" t="s">
         <v>92</v>
       </c>
+      <c r="G42" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H42" t="s">
+        <v>1389</v>
+      </c>
       <c r="I42" t="s">
         <v>2612</v>
       </c>
@@ -10760,7 +11044,7 @@
         <v>1389</v>
       </c>
       <c r="I43" t="s">
-        <v>2628</v>
+        <v>2626</v>
       </c>
       <c r="K43" s="8" t="s">
         <v>2549</v>
@@ -10801,7 +11085,7 @@
         <v>1389</v>
       </c>
       <c r="I44" t="s">
-        <v>2626</v>
+        <v>2624</v>
       </c>
       <c r="K44" s="8" t="s">
         <v>2549</v>
@@ -10878,7 +11162,7 @@
         <v>1394</v>
       </c>
       <c r="I46" t="s">
-        <v>2626</v>
+        <v>2624</v>
       </c>
       <c r="K46" s="8" t="s">
         <v>2552</v>
@@ -10903,12 +11187,21 @@
       <c r="C47" t="s">
         <v>1676</v>
       </c>
+      <c r="D47" t="s">
+        <v>2194</v>
+      </c>
       <c r="E47" t="s">
         <v>104</v>
       </c>
       <c r="F47" t="s">
         <v>105</v>
       </c>
+      <c r="G47" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H47" t="s">
+        <v>2656</v>
+      </c>
       <c r="I47" t="s">
         <v>2612</v>
       </c>
@@ -10932,12 +11225,21 @@
       <c r="C48" t="s">
         <v>1676</v>
       </c>
+      <c r="D48" t="s">
+        <v>2194</v>
+      </c>
       <c r="E48" t="s">
         <v>104</v>
       </c>
       <c r="F48" t="s">
         <v>107</v>
       </c>
+      <c r="G48" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H48" t="s">
+        <v>2656</v>
+      </c>
       <c r="I48" t="s">
         <v>2612</v>
       </c>
@@ -10977,7 +11279,7 @@
         <v>1400</v>
       </c>
       <c r="I49" t="s">
-        <v>2626</v>
+        <v>2624</v>
       </c>
       <c r="J49" s="8" t="s">
         <v>2555</v>
@@ -11002,13 +11304,22 @@
       <c r="C50" t="s">
         <v>1676</v>
       </c>
+      <c r="D50" t="s">
+        <v>2194</v>
+      </c>
       <c r="E50" t="s">
         <v>104</v>
       </c>
       <c r="F50" t="s">
         <v>111</v>
       </c>
-      <c r="I50" s="15" t="s">
+      <c r="G50" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H50" t="s">
+        <v>2656</v>
+      </c>
+      <c r="I50" s="14" t="s">
         <v>2612</v>
       </c>
       <c r="J50" s="11" t="s">
@@ -11047,7 +11358,7 @@
         <v>1400</v>
       </c>
       <c r="I51" t="s">
-        <v>2628</v>
+        <v>2626</v>
       </c>
       <c r="J51" s="8" t="s">
         <v>2555</v>
@@ -11072,13 +11383,22 @@
       <c r="C52" t="s">
         <v>1676</v>
       </c>
+      <c r="D52" t="s">
+        <v>2194</v>
+      </c>
       <c r="E52" t="s">
         <v>104</v>
       </c>
       <c r="F52" t="s">
         <v>115</v>
       </c>
-      <c r="I52" s="15" t="s">
+      <c r="G52" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H52" t="s">
+        <v>2656</v>
+      </c>
+      <c r="I52" s="14" t="s">
         <v>2612</v>
       </c>
       <c r="J52" s="11" t="s">
@@ -11117,7 +11437,7 @@
         <v>1400</v>
       </c>
       <c r="I53" t="s">
-        <v>2626</v>
+        <v>2624</v>
       </c>
       <c r="J53" s="8" t="s">
         <v>2555</v>
@@ -11142,8 +11462,17 @@
       <c r="C54" t="s">
         <v>1350</v>
       </c>
+      <c r="D54" t="s">
+        <v>2638</v>
+      </c>
       <c r="E54" t="s">
         <v>2199</v>
+      </c>
+      <c r="G54" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H54" t="s">
+        <v>2657</v>
       </c>
       <c r="I54" t="s">
         <v>2617</v>
@@ -11162,8 +11491,17 @@
       <c r="C55" t="s">
         <v>1350</v>
       </c>
+      <c r="D55" t="s">
+        <v>2638</v>
+      </c>
       <c r="E55" t="s">
         <v>2199</v>
+      </c>
+      <c r="G55" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H55" t="s">
+        <v>2657</v>
       </c>
       <c r="I55" t="s">
         <v>2617</v>
@@ -11182,8 +11520,17 @@
       <c r="C56" t="s">
         <v>1350</v>
       </c>
+      <c r="D56" t="s">
+        <v>2638</v>
+      </c>
       <c r="E56" t="s">
         <v>2199</v>
+      </c>
+      <c r="G56" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H56" t="s">
+        <v>2657</v>
       </c>
       <c r="I56" t="s">
         <v>2617</v>
@@ -11202,8 +11549,17 @@
       <c r="C57" t="s">
         <v>1350</v>
       </c>
+      <c r="D57" t="s">
+        <v>2638</v>
+      </c>
       <c r="E57" t="s">
         <v>2199</v>
+      </c>
+      <c r="G57" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H57" t="s">
+        <v>2657</v>
       </c>
       <c r="I57" t="s">
         <v>2617</v>
@@ -11222,8 +11578,17 @@
       <c r="C58" t="s">
         <v>1350</v>
       </c>
+      <c r="D58" t="s">
+        <v>2638</v>
+      </c>
       <c r="E58" t="s">
         <v>2199</v>
+      </c>
+      <c r="G58" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H58" t="s">
+        <v>2657</v>
       </c>
       <c r="I58" t="s">
         <v>2617</v>
@@ -11242,8 +11607,17 @@
       <c r="C59" t="s">
         <v>1350</v>
       </c>
+      <c r="D59" t="s">
+        <v>2638</v>
+      </c>
       <c r="E59" t="s">
         <v>2199</v>
+      </c>
+      <c r="G59" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H59" t="s">
+        <v>2657</v>
       </c>
       <c r="I59" t="s">
         <v>2617</v>
@@ -11262,8 +11636,17 @@
       <c r="C60" t="s">
         <v>1350</v>
       </c>
+      <c r="D60" t="s">
+        <v>2638</v>
+      </c>
       <c r="E60" t="s">
         <v>2199</v>
+      </c>
+      <c r="G60" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H60" t="s">
+        <v>2657</v>
       </c>
       <c r="I60" t="s">
         <v>2617</v>
@@ -11282,9 +11665,18 @@
       <c r="C61" t="s">
         <v>1350</v>
       </c>
+      <c r="D61" t="s">
+        <v>2638</v>
+      </c>
       <c r="E61" t="s">
         <v>2199</v>
       </c>
+      <c r="G61" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H61" t="s">
+        <v>2657</v>
+      </c>
       <c r="I61" t="s">
         <v>2617</v>
       </c>
@@ -11312,7 +11704,7 @@
         <v>1402</v>
       </c>
       <c r="I62" t="s">
-        <v>2626</v>
+        <v>2624</v>
       </c>
       <c r="L62" s="5">
         <v>45292</v>
@@ -11344,7 +11736,7 @@
         <v>2207</v>
       </c>
       <c r="I63" t="s">
-        <v>2627</v>
+        <v>2625</v>
       </c>
       <c r="L63" s="5">
         <v>45292</v>
@@ -11436,8 +11828,8 @@
       <c r="G66" t="s">
         <v>2207</v>
       </c>
-      <c r="I66" s="14" t="s">
-        <v>2628</v>
+      <c r="I66" t="s">
+        <v>2626</v>
       </c>
       <c r="K66" s="6" t="s">
         <v>1427</v>
@@ -11459,13 +11851,22 @@
       <c r="C67" t="s">
         <v>1676</v>
       </c>
+      <c r="D67" t="s">
+        <v>2640</v>
+      </c>
       <c r="E67" t="s">
         <v>133</v>
       </c>
       <c r="F67" t="s">
         <v>134</v>
       </c>
-      <c r="I67" s="14" t="s">
+      <c r="G67" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H67" t="s">
+        <v>1677</v>
+      </c>
+      <c r="I67" t="s">
         <v>2612</v>
       </c>
       <c r="J67" t="s">
@@ -11488,13 +11889,22 @@
       <c r="C68" t="s">
         <v>1676</v>
       </c>
+      <c r="D68" t="s">
+        <v>2640</v>
+      </c>
       <c r="E68" t="s">
         <v>133</v>
       </c>
       <c r="F68" t="s">
         <v>136</v>
       </c>
-      <c r="I68" s="14" t="s">
+      <c r="G68" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H68" t="s">
+        <v>1677</v>
+      </c>
+      <c r="I68" t="s">
         <v>2612</v>
       </c>
       <c r="J68" t="s">
@@ -11517,13 +11927,22 @@
       <c r="C69" t="s">
         <v>1676</v>
       </c>
+      <c r="D69" t="s">
+        <v>2640</v>
+      </c>
       <c r="E69" t="s">
         <v>133</v>
       </c>
       <c r="F69" t="s">
         <v>138</v>
       </c>
-      <c r="I69" s="14" t="s">
+      <c r="G69" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H69" t="s">
+        <v>1677</v>
+      </c>
+      <c r="I69" t="s">
         <v>2612</v>
       </c>
       <c r="J69" t="s">
@@ -11546,13 +11965,22 @@
       <c r="C70" t="s">
         <v>1676</v>
       </c>
+      <c r="D70" t="s">
+        <v>2640</v>
+      </c>
       <c r="E70" t="s">
         <v>133</v>
       </c>
       <c r="F70" t="s">
         <v>140</v>
       </c>
-      <c r="I70" s="14" t="s">
+      <c r="G70" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H70" t="s">
+        <v>1677</v>
+      </c>
+      <c r="I70" t="s">
         <v>2612</v>
       </c>
       <c r="J70" t="s">
@@ -11575,13 +12003,22 @@
       <c r="C71" t="s">
         <v>1676</v>
       </c>
+      <c r="D71" t="s">
+        <v>2639</v>
+      </c>
       <c r="E71" t="s">
         <v>142</v>
       </c>
       <c r="F71" t="s">
         <v>143</v>
       </c>
-      <c r="I71" s="14" t="s">
+      <c r="G71" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H71" t="s">
+        <v>1677</v>
+      </c>
+      <c r="I71" t="s">
         <v>2612</v>
       </c>
       <c r="J71" t="s">
@@ -11604,13 +12041,22 @@
       <c r="C72" t="s">
         <v>1676</v>
       </c>
+      <c r="D72" t="s">
+        <v>2639</v>
+      </c>
       <c r="E72" t="s">
         <v>142</v>
       </c>
       <c r="F72" t="s">
         <v>145</v>
       </c>
-      <c r="I72" s="14" t="s">
+      <c r="G72" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H72" t="s">
+        <v>1677</v>
+      </c>
+      <c r="I72" t="s">
         <v>2612</v>
       </c>
       <c r="J72" t="s">
@@ -11648,8 +12094,8 @@
       <c r="H73" t="s">
         <v>1677</v>
       </c>
-      <c r="I73" s="14" t="s">
-        <v>2626</v>
+      <c r="I73" t="s">
+        <v>2624</v>
       </c>
       <c r="J73" s="8" t="s">
         <v>2555</v>
@@ -11677,13 +12123,22 @@
       <c r="C74" t="s">
         <v>1676</v>
       </c>
+      <c r="D74" t="s">
+        <v>2639</v>
+      </c>
       <c r="E74" t="s">
         <v>142</v>
       </c>
       <c r="F74" t="s">
         <v>149</v>
       </c>
-      <c r="I74" s="15" t="s">
+      <c r="G74" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H74" t="s">
+        <v>1677</v>
+      </c>
+      <c r="I74" s="14" t="s">
         <v>2612</v>
       </c>
       <c r="J74" t="s">
@@ -11721,8 +12176,8 @@
       <c r="H75" t="s">
         <v>1677</v>
       </c>
-      <c r="I75" s="14" t="s">
-        <v>2626</v>
+      <c r="I75" t="s">
+        <v>2624</v>
       </c>
       <c r="J75" s="8" t="s">
         <v>2555</v>
@@ -11750,13 +12205,22 @@
       <c r="C76" t="s">
         <v>1676</v>
       </c>
+      <c r="D76" t="s">
+        <v>2639</v>
+      </c>
       <c r="E76" t="s">
         <v>142</v>
       </c>
       <c r="F76" t="s">
         <v>153</v>
       </c>
-      <c r="I76" s="15" t="s">
+      <c r="G76" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H76" t="s">
+        <v>1677</v>
+      </c>
+      <c r="I76" s="14" t="s">
         <v>2612</v>
       </c>
       <c r="J76" t="s">
@@ -11794,8 +12258,8 @@
       <c r="H77" t="s">
         <v>1677</v>
       </c>
-      <c r="I77" s="14" t="s">
-        <v>2628</v>
+      <c r="I77" t="s">
+        <v>2626</v>
       </c>
       <c r="J77" s="8" t="s">
         <v>2555</v>
@@ -12519,7 +12983,7 @@
         <v>2207</v>
       </c>
       <c r="I106" t="s">
-        <v>2628</v>
+        <v>2626</v>
       </c>
       <c r="L106" s="5">
         <v>45292</v>
@@ -12586,7 +13050,7 @@
         <v>1394</v>
       </c>
       <c r="I108" t="s">
-        <v>2626</v>
+        <v>2624</v>
       </c>
       <c r="K108" t="s">
         <v>2558</v>
@@ -12627,7 +13091,7 @@
         <v>1394</v>
       </c>
       <c r="I109" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="K109" t="s">
         <v>2559</v>
@@ -12668,7 +13132,7 @@
         <v>1394</v>
       </c>
       <c r="I110" t="s">
-        <v>2626</v>
+        <v>2624</v>
       </c>
       <c r="K110" t="s">
         <v>2559</v>
@@ -12709,7 +13173,7 @@
         <v>1394</v>
       </c>
       <c r="I111" t="s">
-        <v>2628</v>
+        <v>2626</v>
       </c>
       <c r="K111" t="s">
         <v>2559</v>
@@ -12747,7 +13211,7 @@
         <v>1390</v>
       </c>
       <c r="I112" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
       <c r="K112" s="8" t="s">
         <v>2560</v>
@@ -12782,7 +13246,7 @@
         <v>1390</v>
       </c>
       <c r="I113" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
       <c r="K113" s="8" t="s">
         <v>2560</v>
@@ -12817,7 +13281,7 @@
         <v>1390</v>
       </c>
       <c r="I114" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
       <c r="K114" s="8" t="s">
         <v>2560</v>
@@ -12852,7 +13316,7 @@
         <v>1390</v>
       </c>
       <c r="I115" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
       <c r="K115" s="8" t="s">
         <v>2560</v>
@@ -12887,7 +13351,7 @@
         <v>1390</v>
       </c>
       <c r="I116" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
       <c r="K116" s="8" t="s">
         <v>2560</v>
@@ -12922,7 +13386,7 @@
         <v>1390</v>
       </c>
       <c r="I117" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
       <c r="K117" s="8" t="s">
         <v>2560</v>
@@ -12957,7 +13421,7 @@
         <v>1390</v>
       </c>
       <c r="I118" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
       <c r="K118" s="8" t="s">
         <v>2560</v>
@@ -12992,7 +13456,7 @@
         <v>1390</v>
       </c>
       <c r="I119" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
       <c r="K119" s="8" t="s">
         <v>2560</v>
@@ -13027,7 +13491,7 @@
         <v>1390</v>
       </c>
       <c r="I120" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
       <c r="K120" s="8" t="s">
         <v>2560</v>
@@ -13062,7 +13526,7 @@
         <v>1390</v>
       </c>
       <c r="I121" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
       <c r="K121" s="8" t="s">
         <v>2560</v>
@@ -13097,7 +13561,7 @@
         <v>1390</v>
       </c>
       <c r="I122" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
       <c r="K122" s="8" t="s">
         <v>2560</v>
@@ -13123,7 +13587,7 @@
       <c r="K123" s="10"/>
       <c r="L123" s="5"/>
       <c r="O123" s="1" t="s">
-        <v>2635</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.2">
@@ -13149,7 +13613,7 @@
         <v>1390</v>
       </c>
       <c r="I124" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
       <c r="K124" s="8" t="s">
         <v>2560</v>
@@ -13201,7 +13665,7 @@
         <v>1390</v>
       </c>
       <c r="I126" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
       <c r="K126" s="8" t="s">
         <v>2560</v>
@@ -13236,7 +13700,7 @@
         <v>1390</v>
       </c>
       <c r="I127" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
       <c r="K127" s="8" t="s">
         <v>2560</v>
@@ -13271,7 +13735,7 @@
         <v>1390</v>
       </c>
       <c r="I128" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
       <c r="K128" s="8" t="s">
         <v>2560</v>
@@ -13306,7 +13770,7 @@
         <v>1390</v>
       </c>
       <c r="I129" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
       <c r="K129" s="8" t="s">
         <v>2560</v>
@@ -13341,7 +13805,7 @@
         <v>1390</v>
       </c>
       <c r="I130" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
       <c r="K130" s="8" t="s">
         <v>2560</v>
@@ -13376,7 +13840,7 @@
         <v>1390</v>
       </c>
       <c r="I131" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
       <c r="K131" s="8" t="s">
         <v>2560</v>
@@ -13411,7 +13875,7 @@
         <v>1390</v>
       </c>
       <c r="I132" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
       <c r="K132" s="8" t="s">
         <v>2560</v>
@@ -14243,12 +14707,21 @@
       <c r="C182" t="s">
         <v>1350</v>
       </c>
+      <c r="D182" t="s">
+        <v>2641</v>
+      </c>
       <c r="E182" t="s">
         <v>298</v>
       </c>
       <c r="F182" t="s">
         <v>299</v>
       </c>
+      <c r="G182" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H182" t="s">
+        <v>1394</v>
+      </c>
       <c r="I182" t="s">
         <v>2612</v>
       </c>
@@ -14285,7 +14758,7 @@
         <v>1389</v>
       </c>
       <c r="I183" t="s">
-        <v>2628</v>
+        <v>2626</v>
       </c>
       <c r="K183" t="s">
         <v>2561</v>
@@ -14310,12 +14783,21 @@
       <c r="C184" t="s">
         <v>1350</v>
       </c>
+      <c r="D184" t="s">
+        <v>2641</v>
+      </c>
       <c r="E184" t="s">
         <v>298</v>
       </c>
       <c r="F184" t="s">
         <v>303</v>
       </c>
+      <c r="G184" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H184" t="s">
+        <v>1394</v>
+      </c>
       <c r="I184" t="s">
         <v>2612</v>
       </c>
@@ -14352,7 +14834,7 @@
         <v>1389</v>
       </c>
       <c r="I185" t="s">
-        <v>2626</v>
+        <v>2624</v>
       </c>
       <c r="K185" t="s">
         <v>2561</v>
@@ -14377,12 +14859,21 @@
       <c r="C186" t="s">
         <v>1350</v>
       </c>
+      <c r="D186" t="s">
+        <v>2641</v>
+      </c>
       <c r="E186" t="s">
         <v>298</v>
       </c>
       <c r="F186" t="s">
         <v>307</v>
       </c>
+      <c r="G186" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H186" t="s">
+        <v>1394</v>
+      </c>
       <c r="I186" t="s">
         <v>2612</v>
       </c>
@@ -14403,12 +14894,21 @@
       <c r="C187" t="s">
         <v>1350</v>
       </c>
+      <c r="D187" t="s">
+        <v>2641</v>
+      </c>
       <c r="E187" t="s">
         <v>298</v>
       </c>
       <c r="F187" t="s">
         <v>309</v>
       </c>
+      <c r="G187" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H187" t="s">
+        <v>1394</v>
+      </c>
       <c r="I187" t="s">
         <v>2612</v>
       </c>
@@ -14475,7 +14975,7 @@
         <v>1803</v>
       </c>
       <c r="I189" t="s">
-        <v>2628</v>
+        <v>2626</v>
       </c>
       <c r="K189" s="8" t="s">
         <v>2563</v>
@@ -14510,7 +15010,7 @@
         <v>1390</v>
       </c>
       <c r="I190" t="s">
-        <v>2631</v>
+        <v>2629</v>
       </c>
       <c r="K190" s="8" t="s">
         <v>2564</v>
@@ -14551,7 +15051,7 @@
         <v>2220</v>
       </c>
       <c r="I191" t="s">
-        <v>2622</v>
+        <v>2621</v>
       </c>
       <c r="K191" t="s">
         <v>2565</v>
@@ -14756,7 +15256,7 @@
         <v>2220</v>
       </c>
       <c r="I196" t="s">
-        <v>2622</v>
+        <v>2621</v>
       </c>
       <c r="K196" t="s">
         <v>2565</v>
@@ -14797,7 +15297,7 @@
         <v>2220</v>
       </c>
       <c r="I197" t="s">
-        <v>2627</v>
+        <v>2625</v>
       </c>
       <c r="K197" t="s">
         <v>2565</v>
@@ -15166,7 +15666,7 @@
         <v>2220</v>
       </c>
       <c r="I206" t="s">
-        <v>2627</v>
+        <v>2625</v>
       </c>
       <c r="K206" t="s">
         <v>2565</v>
@@ -15412,7 +15912,7 @@
         <v>2220</v>
       </c>
       <c r="I212" t="s">
-        <v>2627</v>
+        <v>2625</v>
       </c>
       <c r="K212" t="s">
         <v>2565</v>
@@ -15576,7 +16076,7 @@
         <v>2220</v>
       </c>
       <c r="I216" s="13" t="s">
-        <v>2627</v>
+        <v>2625</v>
       </c>
       <c r="K216" t="s">
         <v>2565</v>
@@ -15945,7 +16445,7 @@
         <v>2220</v>
       </c>
       <c r="I225" t="s">
-        <v>2627</v>
+        <v>2625</v>
       </c>
       <c r="K225" t="s">
         <v>2565</v>
@@ -16027,7 +16527,7 @@
         <v>2220</v>
       </c>
       <c r="I227" t="s">
-        <v>2627</v>
+        <v>2625</v>
       </c>
       <c r="K227" t="s">
         <v>2565</v>
@@ -16068,7 +16568,7 @@
         <v>2220</v>
       </c>
       <c r="I228" t="s">
-        <v>2622</v>
+        <v>2621</v>
       </c>
       <c r="K228" t="s">
         <v>2565</v>
@@ -16231,6 +16731,9 @@
       <c r="H232" t="s">
         <v>1860</v>
       </c>
+      <c r="I232" t="s">
+        <v>2624</v>
+      </c>
       <c r="K232" s="8" t="s">
         <v>2566</v>
       </c>
@@ -16254,12 +16757,24 @@
       <c r="C233" t="s">
         <v>1350</v>
       </c>
+      <c r="D233" t="s">
+        <v>2642</v>
+      </c>
       <c r="E233" t="s">
         <v>404</v>
       </c>
       <c r="F233" t="s">
         <v>405</v>
       </c>
+      <c r="G233" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H233" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I233" t="s">
+        <v>2612</v>
+      </c>
       <c r="K233" t="s">
         <v>2568</v>
       </c>
@@ -16292,6 +16807,9 @@
       <c r="H234" t="s">
         <v>1855</v>
       </c>
+      <c r="I234" t="s">
+        <v>2626</v>
+      </c>
       <c r="K234" s="8" t="s">
         <v>2567</v>
       </c>
@@ -16330,6 +16848,9 @@
       <c r="H235" t="s">
         <v>1855</v>
       </c>
+      <c r="I235" t="s">
+        <v>2626</v>
+      </c>
       <c r="K235" s="8" t="s">
         <v>2567</v>
       </c>
@@ -16368,6 +16889,9 @@
       <c r="H236" t="s">
         <v>1389</v>
       </c>
+      <c r="I236" t="s">
+        <v>2626</v>
+      </c>
       <c r="K236" t="s">
         <v>2570</v>
       </c>
@@ -16403,6 +16927,9 @@
       <c r="H237" t="s">
         <v>1389</v>
       </c>
+      <c r="I237" t="s">
+        <v>2624</v>
+      </c>
       <c r="K237" t="s">
         <v>2570</v>
       </c>
@@ -16441,6 +16968,9 @@
       <c r="H238" t="s">
         <v>1389</v>
       </c>
+      <c r="I238" t="s">
+        <v>2624</v>
+      </c>
       <c r="K238" t="s">
         <v>2551</v>
       </c>
@@ -16479,6 +17009,9 @@
       <c r="H239" t="s">
         <v>1389</v>
       </c>
+      <c r="I239" t="s">
+        <v>2626</v>
+      </c>
       <c r="K239" t="s">
         <v>2552</v>
       </c>
@@ -16502,12 +17035,24 @@
       <c r="C240" t="s">
         <v>1676</v>
       </c>
+      <c r="D240" t="s">
+        <v>2643</v>
+      </c>
       <c r="E240" t="s">
         <v>420</v>
       </c>
       <c r="F240" t="s">
         <v>421</v>
       </c>
+      <c r="G240" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H240" t="s">
+        <v>1389</v>
+      </c>
+      <c r="I240" t="s">
+        <v>2613</v>
+      </c>
       <c r="J240" t="s">
         <v>2572</v>
       </c>
@@ -16528,12 +17073,24 @@
       <c r="C241" t="s">
         <v>1676</v>
       </c>
+      <c r="D241" t="s">
+        <v>2643</v>
+      </c>
       <c r="E241" t="s">
         <v>420</v>
       </c>
       <c r="F241" t="s">
         <v>423</v>
       </c>
+      <c r="G241" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H241" t="s">
+        <v>1389</v>
+      </c>
+      <c r="I241" t="s">
+        <v>2613</v>
+      </c>
       <c r="J241" t="s">
         <v>2573</v>
       </c>
@@ -16554,12 +17111,24 @@
       <c r="C242" t="s">
         <v>1676</v>
       </c>
+      <c r="D242" t="s">
+        <v>2643</v>
+      </c>
       <c r="E242" t="s">
         <v>420</v>
       </c>
       <c r="F242" t="s">
         <v>425</v>
       </c>
+      <c r="G242" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H242" t="s">
+        <v>1389</v>
+      </c>
+      <c r="I242" t="s">
+        <v>2613</v>
+      </c>
       <c r="J242" t="s">
         <v>2574</v>
       </c>
@@ -16580,12 +17149,24 @@
       <c r="C243" t="s">
         <v>1676</v>
       </c>
+      <c r="D243" t="s">
+        <v>2643</v>
+      </c>
       <c r="E243" t="s">
         <v>420</v>
       </c>
       <c r="F243" t="s">
         <v>427</v>
       </c>
+      <c r="G243" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H243" t="s">
+        <v>1389</v>
+      </c>
+      <c r="I243" t="s">
+        <v>2613</v>
+      </c>
       <c r="J243" t="s">
         <v>2575</v>
       </c>
@@ -16606,12 +17187,24 @@
       <c r="C244" t="s">
         <v>1676</v>
       </c>
+      <c r="D244" t="s">
+        <v>2643</v>
+      </c>
       <c r="E244" t="s">
         <v>420</v>
       </c>
       <c r="F244" t="s">
         <v>429</v>
       </c>
+      <c r="G244" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H244" t="s">
+        <v>1389</v>
+      </c>
+      <c r="I244" t="s">
+        <v>2613</v>
+      </c>
       <c r="J244" t="s">
         <v>2576</v>
       </c>
@@ -16632,12 +17225,24 @@
       <c r="C245" t="s">
         <v>1676</v>
       </c>
+      <c r="D245" t="s">
+        <v>2643</v>
+      </c>
       <c r="E245" t="s">
         <v>420</v>
       </c>
       <c r="F245" t="s">
         <v>431</v>
       </c>
+      <c r="G245" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H245" t="s">
+        <v>1389</v>
+      </c>
+      <c r="I245" t="s">
+        <v>2613</v>
+      </c>
       <c r="J245" t="s">
         <v>2577</v>
       </c>
@@ -16658,12 +17263,24 @@
       <c r="C246" t="s">
         <v>1676</v>
       </c>
+      <c r="D246" t="s">
+        <v>2643</v>
+      </c>
       <c r="E246" t="s">
         <v>433</v>
       </c>
       <c r="F246" t="s">
         <v>434</v>
       </c>
+      <c r="G246" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H246" t="s">
+        <v>1868</v>
+      </c>
+      <c r="I246" t="s">
+        <v>2613</v>
+      </c>
       <c r="J246" t="s">
         <v>2555</v>
       </c>
@@ -16699,6 +17316,9 @@
       <c r="H247" t="s">
         <v>1868</v>
       </c>
+      <c r="I247" t="s">
+        <v>2624</v>
+      </c>
       <c r="J247" s="8" t="s">
         <v>2555</v>
       </c>
@@ -16725,12 +17345,24 @@
       <c r="C248" t="s">
         <v>1676</v>
       </c>
+      <c r="D248" t="s">
+        <v>2227</v>
+      </c>
       <c r="E248" t="s">
         <v>433</v>
       </c>
       <c r="F248" t="s">
         <v>439</v>
       </c>
+      <c r="G248" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H248" t="s">
+        <v>1868</v>
+      </c>
+      <c r="I248" t="s">
+        <v>2613</v>
+      </c>
       <c r="J248" t="s">
         <v>2555</v>
       </c>
@@ -16766,6 +17398,9 @@
       <c r="H249" t="s">
         <v>1868</v>
       </c>
+      <c r="I249" t="s">
+        <v>2626</v>
+      </c>
       <c r="J249" s="8" t="s">
         <v>2555</v>
       </c>
@@ -16792,12 +17427,24 @@
       <c r="C250" t="s">
         <v>1676</v>
       </c>
+      <c r="D250" t="s">
+        <v>2227</v>
+      </c>
       <c r="E250" t="s">
         <v>433</v>
       </c>
       <c r="F250" t="s">
         <v>443</v>
       </c>
+      <c r="G250" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H250" t="s">
+        <v>1868</v>
+      </c>
+      <c r="I250" t="s">
+        <v>2613</v>
+      </c>
       <c r="J250" t="s">
         <v>2555</v>
       </c>
@@ -16833,6 +17480,9 @@
       <c r="H251" t="s">
         <v>1868</v>
       </c>
+      <c r="I251" t="s">
+        <v>2624</v>
+      </c>
       <c r="J251" s="8" t="s">
         <v>2555</v>
       </c>
@@ -16859,12 +17509,24 @@
       <c r="C252" t="s">
         <v>1676</v>
       </c>
+      <c r="D252" t="s">
+        <v>2227</v>
+      </c>
       <c r="E252" t="s">
         <v>433</v>
       </c>
       <c r="F252" t="s">
         <v>447</v>
       </c>
+      <c r="G252" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H252" t="s">
+        <v>1868</v>
+      </c>
+      <c r="I252" t="s">
+        <v>2613</v>
+      </c>
       <c r="J252" t="s">
         <v>2555</v>
       </c>
@@ -16900,6 +17562,9 @@
       <c r="H253" t="s">
         <v>1868</v>
       </c>
+      <c r="I253" t="s">
+        <v>2624</v>
+      </c>
       <c r="J253" s="8" t="s">
         <v>2555</v>
       </c>
@@ -16926,12 +17591,24 @@
       <c r="C254" t="s">
         <v>1676</v>
       </c>
+      <c r="D254" t="s">
+        <v>2227</v>
+      </c>
       <c r="E254" t="s">
         <v>433</v>
       </c>
       <c r="F254" t="s">
         <v>451</v>
       </c>
+      <c r="G254" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H254" t="s">
+        <v>1868</v>
+      </c>
+      <c r="I254" t="s">
+        <v>2613</v>
+      </c>
       <c r="J254" t="s">
         <v>2555</v>
       </c>
@@ -16967,6 +17644,9 @@
       <c r="H255" t="s">
         <v>1868</v>
       </c>
+      <c r="I255" t="s">
+        <v>2624</v>
+      </c>
       <c r="J255" s="8" t="s">
         <v>2555</v>
       </c>
@@ -17002,6 +17682,9 @@
       <c r="G256" t="s">
         <v>1788</v>
       </c>
+      <c r="H256" t="s">
+        <v>1868</v>
+      </c>
       <c r="K256" s="8" t="s">
         <v>2548</v>
       </c>
@@ -17037,6 +17720,9 @@
       <c r="H257" t="s">
         <v>1868</v>
       </c>
+      <c r="I257" t="s">
+        <v>2626</v>
+      </c>
       <c r="K257" s="8" t="s">
         <v>2578</v>
       </c>
@@ -17075,6 +17761,9 @@
       <c r="H258" t="s">
         <v>1868</v>
       </c>
+      <c r="I258" t="s">
+        <v>2624</v>
+      </c>
       <c r="K258" s="8" t="s">
         <v>2578</v>
       </c>
@@ -17148,6 +17837,9 @@
       <c r="H260" t="s">
         <v>1389</v>
       </c>
+      <c r="I260" t="s">
+        <v>2626</v>
+      </c>
       <c r="K260" s="8" t="s">
         <v>2580</v>
       </c>
@@ -17183,6 +17875,9 @@
       <c r="H261" t="s">
         <v>1400</v>
       </c>
+      <c r="I261" t="s">
+        <v>2626</v>
+      </c>
       <c r="K261" s="8" t="s">
         <v>2580</v>
       </c>
@@ -17217,11 +17912,17 @@
       <c r="C263" t="s">
         <v>1350</v>
       </c>
+      <c r="D263" t="s">
+        <v>2234</v>
+      </c>
       <c r="E263" t="s">
         <v>470</v>
       </c>
       <c r="F263" t="s">
         <v>321</v>
+      </c>
+      <c r="G263" t="s">
+        <v>1854</v>
       </c>
       <c r="I263" t="s">
         <v>2613</v>
@@ -17244,11 +17945,17 @@
       <c r="C264" t="s">
         <v>1350</v>
       </c>
+      <c r="D264" t="s">
+        <v>2234</v>
+      </c>
       <c r="E264" t="s">
         <v>470</v>
       </c>
       <c r="F264" t="s">
         <v>323</v>
+      </c>
+      <c r="G264" t="s">
+        <v>1854</v>
       </c>
       <c r="I264" t="s">
         <v>2614</v>
@@ -17271,11 +17978,17 @@
       <c r="C265" t="s">
         <v>1350</v>
       </c>
+      <c r="D265" t="s">
+        <v>2234</v>
+      </c>
       <c r="E265" t="s">
         <v>470</v>
       </c>
       <c r="F265" t="s">
         <v>325</v>
+      </c>
+      <c r="G265" t="s">
+        <v>1854</v>
       </c>
       <c r="I265" t="s">
         <v>2613</v>
@@ -17298,11 +18011,17 @@
       <c r="C266" t="s">
         <v>1350</v>
       </c>
+      <c r="D266" t="s">
+        <v>2234</v>
+      </c>
       <c r="E266" t="s">
         <v>470</v>
       </c>
       <c r="F266" t="s">
         <v>327</v>
+      </c>
+      <c r="G266" t="s">
+        <v>1854</v>
       </c>
       <c r="I266" t="s">
         <v>2614</v>
@@ -17468,6 +18187,9 @@
       <c r="F271" t="s">
         <v>339</v>
       </c>
+      <c r="G271" t="s">
+        <v>1854</v>
+      </c>
       <c r="I271" t="s">
         <v>2613</v>
       </c>
@@ -17547,7 +18269,7 @@
         <v>1855</v>
       </c>
       <c r="I273" t="s">
-        <v>2637</v>
+        <v>2634</v>
       </c>
       <c r="J273" s="8"/>
       <c r="K273" s="8" t="s">
@@ -17579,6 +18301,9 @@
       <c r="F274" t="s">
         <v>345</v>
       </c>
+      <c r="G274" t="s">
+        <v>1854</v>
+      </c>
       <c r="J274" s="8"/>
       <c r="K274" s="8" t="s">
         <v>2565</v>
@@ -17655,7 +18380,7 @@
         <v>1855</v>
       </c>
       <c r="I276" t="s">
-        <v>2627</v>
+        <v>2625</v>
       </c>
       <c r="J276" s="8"/>
       <c r="K276" s="8" t="s">
@@ -17681,11 +18406,17 @@
       <c r="C277" t="s">
         <v>1350</v>
       </c>
+      <c r="D277" t="s">
+        <v>2234</v>
+      </c>
       <c r="E277" t="s">
         <v>470</v>
       </c>
       <c r="F277" t="s">
         <v>351</v>
+      </c>
+      <c r="G277" t="s">
+        <v>1854</v>
       </c>
       <c r="I277" t="s">
         <v>2613</v>
@@ -17708,11 +18439,17 @@
       <c r="C278" t="s">
         <v>1350</v>
       </c>
+      <c r="D278" t="s">
+        <v>2234</v>
+      </c>
       <c r="E278" t="s">
         <v>470</v>
       </c>
       <c r="F278" t="s">
         <v>353</v>
+      </c>
+      <c r="G278" t="s">
+        <v>1854</v>
       </c>
       <c r="I278" t="s">
         <v>2612</v>
@@ -17735,11 +18472,17 @@
       <c r="C279" t="s">
         <v>1350</v>
       </c>
+      <c r="D279" t="s">
+        <v>2234</v>
+      </c>
       <c r="E279" t="s">
         <v>470</v>
       </c>
       <c r="F279" t="s">
         <v>355</v>
+      </c>
+      <c r="G279" t="s">
+        <v>1854</v>
       </c>
       <c r="I279" t="s">
         <v>2615</v>
@@ -17762,11 +18505,17 @@
       <c r="C280" t="s">
         <v>1350</v>
       </c>
+      <c r="D280" t="s">
+        <v>2234</v>
+      </c>
       <c r="E280" t="s">
         <v>470</v>
       </c>
       <c r="F280" t="s">
         <v>357</v>
+      </c>
+      <c r="G280" t="s">
+        <v>1854</v>
       </c>
       <c r="I280" t="s">
         <v>2615</v>
@@ -17847,7 +18596,7 @@
         <v>1855</v>
       </c>
       <c r="I282" t="s">
-        <v>2627</v>
+        <v>2625</v>
       </c>
       <c r="J282" s="8"/>
       <c r="K282" s="8" t="s">
@@ -17873,11 +18622,17 @@
       <c r="C283" t="s">
         <v>1350</v>
       </c>
+      <c r="D283" t="s">
+        <v>2234</v>
+      </c>
       <c r="E283" t="s">
         <v>470</v>
       </c>
       <c r="F283" t="s">
         <v>363</v>
+      </c>
+      <c r="G283" t="s">
+        <v>1854</v>
       </c>
       <c r="I283" t="s">
         <v>2613</v>
@@ -17942,11 +18697,17 @@
       <c r="C285" t="s">
         <v>1350</v>
       </c>
+      <c r="D285" t="s">
+        <v>2234</v>
+      </c>
       <c r="E285" t="s">
         <v>470</v>
       </c>
       <c r="F285" t="s">
         <v>367</v>
+      </c>
+      <c r="G285" t="s">
+        <v>1854</v>
       </c>
       <c r="I285" t="s">
         <v>2614</v>
@@ -17985,7 +18746,7 @@
         <v>1855</v>
       </c>
       <c r="I286" t="s">
-        <v>2627</v>
+        <v>2625</v>
       </c>
       <c r="J286" s="8"/>
       <c r="K286" s="8" t="s">
@@ -18027,7 +18788,7 @@
         <v>1855</v>
       </c>
       <c r="I287" t="s">
-        <v>2627</v>
+        <v>2625</v>
       </c>
       <c r="J287" s="8"/>
       <c r="K287" s="8" t="s">
@@ -18053,11 +18814,17 @@
       <c r="C288" t="s">
         <v>1350</v>
       </c>
+      <c r="D288" t="s">
+        <v>2234</v>
+      </c>
       <c r="E288" t="s">
         <v>470</v>
       </c>
       <c r="F288" t="s">
         <v>371</v>
+      </c>
+      <c r="G288" t="s">
+        <v>1854</v>
       </c>
       <c r="I288" t="s">
         <v>2614</v>
@@ -18080,11 +18847,17 @@
       <c r="C289" t="s">
         <v>1350</v>
       </c>
+      <c r="D289" t="s">
+        <v>2234</v>
+      </c>
       <c r="E289" t="s">
         <v>470</v>
       </c>
       <c r="F289" t="s">
         <v>373</v>
+      </c>
+      <c r="G289" t="s">
+        <v>1854</v>
       </c>
       <c r="I289" t="s">
         <v>2614</v>
@@ -18149,11 +18922,17 @@
       <c r="C291" t="s">
         <v>1350</v>
       </c>
+      <c r="D291" t="s">
+        <v>2234</v>
+      </c>
       <c r="E291" t="s">
         <v>470</v>
       </c>
       <c r="F291" t="s">
         <v>377</v>
+      </c>
+      <c r="G291" t="s">
+        <v>1854</v>
       </c>
       <c r="I291" t="s">
         <v>2613</v>
@@ -18176,11 +18955,17 @@
       <c r="C292" t="s">
         <v>1350</v>
       </c>
+      <c r="D292" t="s">
+        <v>2234</v>
+      </c>
       <c r="E292" t="s">
         <v>470</v>
       </c>
       <c r="F292" t="s">
         <v>379</v>
+      </c>
+      <c r="G292" t="s">
+        <v>1854</v>
       </c>
       <c r="I292" t="s">
         <v>2613</v>
@@ -18203,11 +18988,17 @@
       <c r="C293" t="s">
         <v>1350</v>
       </c>
+      <c r="D293" t="s">
+        <v>2234</v>
+      </c>
       <c r="E293" t="s">
         <v>470</v>
       </c>
       <c r="F293" t="s">
         <v>381</v>
+      </c>
+      <c r="G293" t="s">
+        <v>1854</v>
       </c>
       <c r="I293" t="s">
         <v>2613</v>
@@ -18272,11 +19063,17 @@
       <c r="C295" t="s">
         <v>1350</v>
       </c>
+      <c r="D295" t="s">
+        <v>2234</v>
+      </c>
       <c r="E295" t="s">
         <v>470</v>
       </c>
       <c r="F295" t="s">
         <v>385</v>
+      </c>
+      <c r="G295" t="s">
+        <v>1854</v>
       </c>
       <c r="I295" t="s">
         <v>2613</v>
@@ -18315,7 +19112,7 @@
         <v>1855</v>
       </c>
       <c r="I296" t="s">
-        <v>2627</v>
+        <v>2625</v>
       </c>
       <c r="J296" s="8"/>
       <c r="K296" s="8" t="s">
@@ -18341,11 +19138,17 @@
       <c r="C297" t="s">
         <v>1350</v>
       </c>
+      <c r="D297" t="s">
+        <v>2234</v>
+      </c>
       <c r="E297" t="s">
         <v>470</v>
       </c>
       <c r="F297" t="s">
         <v>389</v>
+      </c>
+      <c r="G297" t="s">
+        <v>1854</v>
       </c>
       <c r="I297" t="s">
         <v>2612</v>
@@ -18384,7 +19187,7 @@
         <v>1855</v>
       </c>
       <c r="I298" t="s">
-        <v>2627</v>
+        <v>2625</v>
       </c>
       <c r="J298" s="8"/>
       <c r="K298" s="8" t="s">
@@ -18427,6 +19230,9 @@
       <c r="F300" t="s">
         <v>395</v>
       </c>
+      <c r="G300" t="s">
+        <v>1854</v>
+      </c>
       <c r="I300" t="s">
         <v>2615</v>
       </c>
@@ -18454,6 +19260,9 @@
       <c r="F301" t="s">
         <v>397</v>
       </c>
+      <c r="G301" t="s">
+        <v>1854</v>
+      </c>
       <c r="I301" t="s">
         <v>2615</v>
       </c>
@@ -18491,7 +19300,7 @@
         <v>1855</v>
       </c>
       <c r="I302" t="s">
-        <v>2636</v>
+        <v>2633</v>
       </c>
       <c r="J302" s="8"/>
       <c r="K302" s="8" t="s">
@@ -18564,7 +19373,9 @@
       <c r="H304" t="s">
         <v>1855</v>
       </c>
-      <c r="I304" s="8"/>
+      <c r="I304" s="8" t="s">
+        <v>2624</v>
+      </c>
       <c r="J304" s="8" t="s">
         <v>2555</v>
       </c>
@@ -18602,6 +19413,9 @@
       </c>
       <c r="H305" t="s">
         <v>1389</v>
+      </c>
+      <c r="I305" t="s">
+        <v>2626</v>
       </c>
       <c r="J305" s="8"/>
       <c r="K305" s="8" t="s">
@@ -18642,7 +19456,9 @@
       <c r="H306" t="s">
         <v>1855</v>
       </c>
-      <c r="I306" s="8"/>
+      <c r="I306" s="8" t="s">
+        <v>2626</v>
+      </c>
       <c r="J306" s="8" t="s">
         <v>2555</v>
       </c>
@@ -18669,12 +19485,24 @@
       <c r="C307" t="s">
         <v>1676</v>
       </c>
+      <c r="D307" t="s">
+        <v>2644</v>
+      </c>
       <c r="E307" t="s">
         <v>404</v>
       </c>
       <c r="F307" t="s">
         <v>518</v>
       </c>
+      <c r="G307" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H307" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I307" t="s">
+        <v>2612</v>
+      </c>
       <c r="J307" t="s">
         <v>2572</v>
       </c>
@@ -18710,7 +19538,9 @@
       <c r="H308" t="s">
         <v>1855</v>
       </c>
-      <c r="I308" s="8"/>
+      <c r="I308" s="8" t="s">
+        <v>2624</v>
+      </c>
       <c r="J308" s="8" t="s">
         <v>2555</v>
       </c>
@@ -18737,12 +19567,24 @@
       <c r="C309" t="s">
         <v>1676</v>
       </c>
+      <c r="D309" t="s">
+        <v>2644</v>
+      </c>
       <c r="E309" t="s">
         <v>404</v>
       </c>
       <c r="F309" t="s">
         <v>522</v>
       </c>
+      <c r="G309" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H309" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I309" t="s">
+        <v>2612</v>
+      </c>
       <c r="J309" t="s">
         <v>2572</v>
       </c>
@@ -18763,12 +19605,24 @@
       <c r="C310" t="s">
         <v>1676</v>
       </c>
+      <c r="D310" t="s">
+        <v>2644</v>
+      </c>
       <c r="E310" t="s">
         <v>404</v>
       </c>
       <c r="F310" t="s">
         <v>524</v>
       </c>
+      <c r="G310" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H310" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I310" s="8" t="s">
+        <v>2612</v>
+      </c>
       <c r="J310" t="s">
         <v>2572</v>
       </c>
@@ -18789,12 +19643,24 @@
       <c r="C311" t="s">
         <v>1676</v>
       </c>
+      <c r="D311" t="s">
+        <v>2644</v>
+      </c>
       <c r="E311" t="s">
         <v>404</v>
       </c>
       <c r="F311" t="s">
         <v>526</v>
       </c>
+      <c r="G311" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H311" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I311" t="s">
+        <v>2612</v>
+      </c>
       <c r="J311" t="s">
         <v>2572</v>
       </c>
@@ -18815,12 +19681,24 @@
       <c r="C312" t="s">
         <v>1676</v>
       </c>
+      <c r="D312" t="s">
+        <v>2644</v>
+      </c>
       <c r="E312" t="s">
         <v>404</v>
       </c>
       <c r="F312" t="s">
         <v>528</v>
       </c>
+      <c r="G312" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H312" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I312" s="8" t="s">
+        <v>2612</v>
+      </c>
       <c r="J312" t="s">
         <v>2572</v>
       </c>
@@ -18841,12 +19719,24 @@
       <c r="C313" t="s">
         <v>1676</v>
       </c>
+      <c r="D313" t="s">
+        <v>2644</v>
+      </c>
       <c r="E313" t="s">
         <v>404</v>
       </c>
       <c r="F313" t="s">
         <v>530</v>
       </c>
+      <c r="G313" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H313" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I313" t="s">
+        <v>2612</v>
+      </c>
       <c r="J313" t="s">
         <v>2572</v>
       </c>
@@ -18867,12 +19757,24 @@
       <c r="C314" t="s">
         <v>1676</v>
       </c>
+      <c r="D314" t="s">
+        <v>2644</v>
+      </c>
       <c r="E314" t="s">
         <v>404</v>
       </c>
       <c r="F314" t="s">
         <v>532</v>
       </c>
+      <c r="G314" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H314" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I314" s="8" t="s">
+        <v>2612</v>
+      </c>
       <c r="J314" t="s">
         <v>2572</v>
       </c>
@@ -18908,7 +19810,9 @@
       <c r="H315" t="s">
         <v>1855</v>
       </c>
-      <c r="I315" s="8"/>
+      <c r="I315" s="8" t="s">
+        <v>2626</v>
+      </c>
       <c r="J315" s="8" t="s">
         <v>2555</v>
       </c>
@@ -18935,12 +19839,24 @@
       <c r="C316" t="s">
         <v>1676</v>
       </c>
+      <c r="D316" t="s">
+        <v>2645</v>
+      </c>
       <c r="E316" t="s">
         <v>536</v>
       </c>
       <c r="F316" t="s">
         <v>537</v>
       </c>
+      <c r="G316" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H316" t="s">
+        <v>1394</v>
+      </c>
+      <c r="I316" t="s">
+        <v>2612</v>
+      </c>
       <c r="J316" t="s">
         <v>2584</v>
       </c>
@@ -18961,12 +19877,24 @@
       <c r="C317" t="s">
         <v>1676</v>
       </c>
+      <c r="D317" t="s">
+        <v>2645</v>
+      </c>
       <c r="E317" t="s">
         <v>536</v>
       </c>
       <c r="F317" t="s">
         <v>539</v>
       </c>
+      <c r="G317" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H317" t="s">
+        <v>1394</v>
+      </c>
+      <c r="I317" t="s">
+        <v>2612</v>
+      </c>
       <c r="J317" t="s">
         <v>2584</v>
       </c>
@@ -18987,11 +19915,23 @@
       <c r="C318" t="s">
         <v>1676</v>
       </c>
+      <c r="D318" t="s">
+        <v>2645</v>
+      </c>
       <c r="E318" t="s">
         <v>536</v>
       </c>
       <c r="F318" t="s">
         <v>541</v>
+      </c>
+      <c r="G318" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H318" t="s">
+        <v>1394</v>
+      </c>
+      <c r="I318" t="s">
+        <v>2612</v>
       </c>
       <c r="J318" t="s">
         <v>2584</v>
@@ -19024,6 +19964,15 @@
       <c r="C320" t="s">
         <v>1350</v>
       </c>
+      <c r="D320" t="s">
+        <v>2646</v>
+      </c>
+      <c r="G320" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H320" t="s">
+        <v>2657</v>
+      </c>
       <c r="I320" t="s">
         <v>2617</v>
       </c>
@@ -19041,6 +19990,15 @@
       <c r="C321" t="s">
         <v>1350</v>
       </c>
+      <c r="D321" t="s">
+        <v>2646</v>
+      </c>
+      <c r="G321" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H321" t="s">
+        <v>2657</v>
+      </c>
       <c r="I321" t="s">
         <v>2617</v>
       </c>
@@ -19058,6 +20016,15 @@
       <c r="C322" t="s">
         <v>1350</v>
       </c>
+      <c r="D322" t="s">
+        <v>2646</v>
+      </c>
+      <c r="G322" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H322" t="s">
+        <v>2657</v>
+      </c>
       <c r="I322" t="s">
         <v>2618</v>
       </c>
@@ -19074,6 +20041,15 @@
       </c>
       <c r="C323" t="s">
         <v>1350</v>
+      </c>
+      <c r="D323" t="s">
+        <v>2646</v>
+      </c>
+      <c r="G323" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H323" t="s">
+        <v>2657</v>
       </c>
       <c r="I323" t="s">
         <v>2617</v>
@@ -19651,6 +20627,9 @@
       <c r="H340" t="s">
         <v>1868</v>
       </c>
+      <c r="I340" t="s">
+        <v>2626</v>
+      </c>
       <c r="J340" s="8" t="s">
         <v>2555</v>
       </c>
@@ -19693,7 +20672,7 @@
         <v>1868</v>
       </c>
       <c r="J341" s="8" t="s">
-        <v>2584</v>
+        <v>2658</v>
       </c>
       <c r="K341" t="s">
         <v>2571</v>
@@ -19727,6 +20706,15 @@
       <c r="F342" t="s">
         <v>570</v>
       </c>
+      <c r="G342" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H342" t="s">
+        <v>1868</v>
+      </c>
+      <c r="I342" t="s">
+        <v>2612</v>
+      </c>
       <c r="J342" t="s">
         <v>2584</v>
       </c>
@@ -19762,6 +20750,9 @@
       <c r="H343" t="s">
         <v>1868</v>
       </c>
+      <c r="I343" t="s">
+        <v>2624</v>
+      </c>
       <c r="J343" s="8" t="s">
         <v>2555</v>
       </c>
@@ -19797,6 +20788,15 @@
       <c r="F344" t="s">
         <v>574</v>
       </c>
+      <c r="G344" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H344" t="s">
+        <v>1868</v>
+      </c>
+      <c r="I344" t="s">
+        <v>2612</v>
+      </c>
       <c r="J344" t="s">
         <v>2584</v>
       </c>
@@ -19832,6 +20832,9 @@
       <c r="H345" t="s">
         <v>1868</v>
       </c>
+      <c r="I345" t="s">
+        <v>2624</v>
+      </c>
       <c r="J345" s="8" t="s">
         <v>2555</v>
       </c>
@@ -19873,6 +20876,9 @@
       <c r="H346" t="s">
         <v>1868</v>
       </c>
+      <c r="I346" t="s">
+        <v>2626</v>
+      </c>
       <c r="K346" t="s">
         <v>2552</v>
       </c>
@@ -19896,12 +20902,24 @@
       <c r="C347" t="s">
         <v>1676</v>
       </c>
+      <c r="D347" t="s">
+        <v>2647</v>
+      </c>
       <c r="E347" t="s">
         <v>580</v>
       </c>
       <c r="F347" t="s">
         <v>581</v>
       </c>
+      <c r="G347" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H347" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I347" t="s">
+        <v>2612</v>
+      </c>
       <c r="J347" t="s">
         <v>2572</v>
       </c>
@@ -19937,6 +20955,9 @@
       <c r="H348" t="s">
         <v>1855</v>
       </c>
+      <c r="I348" t="s">
+        <v>2626</v>
+      </c>
       <c r="J348" s="8" t="s">
         <v>2572</v>
       </c>
@@ -19960,12 +20981,24 @@
       <c r="C349" t="s">
         <v>1676</v>
       </c>
+      <c r="D349" t="s">
+        <v>2647</v>
+      </c>
       <c r="E349" t="s">
         <v>580</v>
       </c>
       <c r="F349" t="s">
         <v>585</v>
       </c>
+      <c r="G349" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H349" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I349" t="s">
+        <v>2612</v>
+      </c>
       <c r="J349" t="s">
         <v>2572</v>
       </c>
@@ -19986,12 +21019,24 @@
       <c r="C350" t="s">
         <v>1676</v>
       </c>
+      <c r="D350" t="s">
+        <v>2647</v>
+      </c>
       <c r="E350" t="s">
         <v>580</v>
       </c>
       <c r="F350" t="s">
         <v>587</v>
       </c>
+      <c r="G350" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H350" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I350" t="s">
+        <v>2612</v>
+      </c>
       <c r="J350" t="s">
         <v>2572</v>
       </c>
@@ -20012,12 +21057,24 @@
       <c r="C351" t="s">
         <v>1676</v>
       </c>
+      <c r="D351" t="s">
+        <v>2647</v>
+      </c>
       <c r="E351" t="s">
         <v>580</v>
       </c>
       <c r="F351" t="s">
         <v>589</v>
       </c>
+      <c r="G351" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H351" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I351" t="s">
+        <v>2612</v>
+      </c>
       <c r="J351" t="s">
         <v>2572</v>
       </c>
@@ -20053,6 +21110,9 @@
       <c r="H352" t="s">
         <v>1855</v>
       </c>
+      <c r="I352" t="s">
+        <v>2626</v>
+      </c>
       <c r="J352" s="8" t="s">
         <v>2572</v>
       </c>
@@ -20079,12 +21139,24 @@
       <c r="C353" t="s">
         <v>1676</v>
       </c>
+      <c r="D353" t="s">
+        <v>2647</v>
+      </c>
       <c r="E353" t="s">
         <v>580</v>
       </c>
       <c r="F353" t="s">
         <v>593</v>
       </c>
+      <c r="G353" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H353" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I353" t="s">
+        <v>2612</v>
+      </c>
       <c r="J353" t="s">
         <v>2572</v>
       </c>
@@ -20120,6 +21192,9 @@
       <c r="H354" t="s">
         <v>1855</v>
       </c>
+      <c r="I354" t="s">
+        <v>2624</v>
+      </c>
       <c r="J354" s="8" t="s">
         <v>2572</v>
       </c>
@@ -20146,12 +21221,24 @@
       <c r="C355" t="s">
         <v>1676</v>
       </c>
+      <c r="D355" t="s">
+        <v>2647</v>
+      </c>
       <c r="E355" t="s">
         <v>580</v>
       </c>
       <c r="F355" t="s">
         <v>597</v>
       </c>
+      <c r="G355" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H355" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I355" t="s">
+        <v>2612</v>
+      </c>
       <c r="J355" t="s">
         <v>2572</v>
       </c>
@@ -20187,6 +21274,9 @@
       <c r="H356" t="s">
         <v>1855</v>
       </c>
+      <c r="I356" t="s">
+        <v>2626</v>
+      </c>
       <c r="J356" s="8" t="s">
         <v>2572</v>
       </c>
@@ -20213,12 +21303,24 @@
       <c r="C357" t="s">
         <v>1676</v>
       </c>
+      <c r="D357" t="s">
+        <v>2647</v>
+      </c>
       <c r="E357" t="s">
         <v>580</v>
       </c>
       <c r="F357" t="s">
         <v>601</v>
       </c>
+      <c r="G357" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H357" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I357" t="s">
+        <v>2612</v>
+      </c>
       <c r="J357" t="s">
         <v>2572</v>
       </c>
@@ -20324,6 +21426,9 @@
       <c r="H360" t="s">
         <v>1389</v>
       </c>
+      <c r="I360" t="s">
+        <v>2624</v>
+      </c>
       <c r="K360" s="8" t="s">
         <v>2549</v>
       </c>
@@ -20362,6 +21467,9 @@
       <c r="H361" t="s">
         <v>1389</v>
       </c>
+      <c r="I361" t="s">
+        <v>2624</v>
+      </c>
       <c r="K361" s="8" t="s">
         <v>2549</v>
       </c>
@@ -20400,6 +21508,9 @@
       <c r="H362" t="s">
         <v>1389</v>
       </c>
+      <c r="I362" t="s">
+        <v>2626</v>
+      </c>
       <c r="K362" s="8" t="s">
         <v>2549</v>
       </c>
@@ -20438,6 +21549,9 @@
       <c r="H363" t="s">
         <v>1860</v>
       </c>
+      <c r="I363" t="s">
+        <v>2624</v>
+      </c>
       <c r="K363" t="s">
         <v>2588</v>
       </c>
@@ -20476,6 +21590,9 @@
       <c r="H364" t="s">
         <v>1860</v>
       </c>
+      <c r="I364" t="s">
+        <v>2620</v>
+      </c>
       <c r="K364" t="s">
         <v>2588</v>
       </c>
@@ -20496,12 +21613,30 @@
       <c r="B365" t="s">
         <v>618</v>
       </c>
+      <c r="C365" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D365" t="s">
+        <v>2648</v>
+      </c>
       <c r="E365" t="s">
         <v>85</v>
       </c>
       <c r="F365" t="s">
         <v>619</v>
       </c>
+      <c r="G365" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H365" t="s">
+        <v>1389</v>
+      </c>
+      <c r="I365" t="s">
+        <v>2612</v>
+      </c>
+      <c r="J365" t="s">
+        <v>2555</v>
+      </c>
       <c r="K365" t="s">
         <v>2589</v>
       </c>
@@ -20516,12 +21651,30 @@
       <c r="B366" t="s">
         <v>620</v>
       </c>
+      <c r="C366" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D366" t="s">
+        <v>2648</v>
+      </c>
       <c r="E366" t="s">
         <v>85</v>
       </c>
       <c r="F366" t="s">
         <v>621</v>
       </c>
+      <c r="G366" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H366" t="s">
+        <v>1389</v>
+      </c>
+      <c r="I366" t="s">
+        <v>2612</v>
+      </c>
+      <c r="J366" t="s">
+        <v>2555</v>
+      </c>
       <c r="K366" t="s">
         <v>2589</v>
       </c>
@@ -20536,12 +21689,30 @@
       <c r="B367" t="s">
         <v>622</v>
       </c>
+      <c r="C367" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D367" t="s">
+        <v>2648</v>
+      </c>
       <c r="E367" t="s">
         <v>85</v>
       </c>
       <c r="F367" t="s">
         <v>623</v>
       </c>
+      <c r="G367" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H367" t="s">
+        <v>1389</v>
+      </c>
+      <c r="I367" t="s">
+        <v>2612</v>
+      </c>
+      <c r="J367" t="s">
+        <v>2555</v>
+      </c>
       <c r="K367" t="s">
         <v>2589</v>
       </c>
@@ -20556,12 +21727,30 @@
       <c r="B368" t="s">
         <v>624</v>
       </c>
+      <c r="C368" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D368" t="s">
+        <v>2648</v>
+      </c>
       <c r="E368" t="s">
         <v>85</v>
       </c>
       <c r="F368" t="s">
         <v>625</v>
       </c>
+      <c r="G368" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H368" t="s">
+        <v>1389</v>
+      </c>
+      <c r="I368" t="s">
+        <v>2612</v>
+      </c>
+      <c r="J368" t="s">
+        <v>2555</v>
+      </c>
       <c r="K368" t="s">
         <v>2589</v>
       </c>
@@ -20569,7 +21758,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="369" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:15" ht="32" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>626</v>
       </c>
@@ -20595,7 +21784,7 @@
         <v>2297</v>
       </c>
     </row>
-    <row r="370" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:15" ht="32" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>626</v>
       </c>
@@ -21410,6 +22599,9 @@
       <c r="H393" t="s">
         <v>1400</v>
       </c>
+      <c r="I393" t="s">
+        <v>2624</v>
+      </c>
       <c r="K393" s="8" t="s">
         <v>2591</v>
       </c>
@@ -21462,12 +22654,27 @@
       <c r="B395" t="s">
         <v>678</v>
       </c>
+      <c r="C395" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D395" t="s">
+        <v>2649</v>
+      </c>
       <c r="E395" t="s">
         <v>679</v>
       </c>
       <c r="F395" t="s">
         <v>680</v>
       </c>
+      <c r="G395" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H395" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I395" t="s">
+        <v>2612</v>
+      </c>
       <c r="J395" t="s">
         <v>2572</v>
       </c>
@@ -21485,12 +22692,27 @@
       <c r="B396" t="s">
         <v>681</v>
       </c>
+      <c r="C396" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D396" t="s">
+        <v>2649</v>
+      </c>
       <c r="E396" t="s">
         <v>679</v>
       </c>
       <c r="F396" t="s">
         <v>682</v>
       </c>
+      <c r="G396" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H396" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I396" t="s">
+        <v>2612</v>
+      </c>
       <c r="J396" t="s">
         <v>2572</v>
       </c>
@@ -21526,6 +22748,9 @@
       <c r="H397" t="s">
         <v>1855</v>
       </c>
+      <c r="I397" t="s">
+        <v>2624</v>
+      </c>
       <c r="J397" s="8" t="s">
         <v>2572</v>
       </c>
@@ -21549,12 +22774,27 @@
       <c r="B398" t="s">
         <v>685</v>
       </c>
+      <c r="C398" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D398" t="s">
+        <v>2649</v>
+      </c>
       <c r="E398" t="s">
         <v>679</v>
       </c>
       <c r="F398" t="s">
         <v>686</v>
       </c>
+      <c r="G398" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H398" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I398" t="s">
+        <v>2612</v>
+      </c>
       <c r="J398" t="s">
         <v>2572</v>
       </c>
@@ -21590,6 +22830,9 @@
       <c r="H399" t="s">
         <v>1855</v>
       </c>
+      <c r="I399" t="s">
+        <v>2626</v>
+      </c>
       <c r="J399" s="8" t="s">
         <v>2572</v>
       </c>
@@ -21613,12 +22856,27 @@
       <c r="B400" t="s">
         <v>688</v>
       </c>
+      <c r="C400" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D400" t="s">
+        <v>2649</v>
+      </c>
       <c r="E400" t="s">
         <v>679</v>
       </c>
       <c r="F400" t="s">
         <v>689</v>
       </c>
+      <c r="G400" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H400" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I400" t="s">
+        <v>2612</v>
+      </c>
       <c r="J400" t="s">
         <v>2572</v>
       </c>
@@ -21654,6 +22912,9 @@
       <c r="H401" t="s">
         <v>1855</v>
       </c>
+      <c r="I401" t="s">
+        <v>2626</v>
+      </c>
       <c r="J401" s="8" t="s">
         <v>2572</v>
       </c>
@@ -21677,12 +22938,27 @@
       <c r="B402" t="s">
         <v>691</v>
       </c>
+      <c r="C402" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D402" t="s">
+        <v>2649</v>
+      </c>
       <c r="E402" t="s">
         <v>679</v>
       </c>
       <c r="F402" t="s">
         <v>692</v>
       </c>
+      <c r="G402" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H402" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I402" t="s">
+        <v>2612</v>
+      </c>
       <c r="J402" t="s">
         <v>2572</v>
       </c>
@@ -21718,6 +22994,9 @@
       <c r="H403" t="s">
         <v>1855</v>
       </c>
+      <c r="I403" t="s">
+        <v>2624</v>
+      </c>
       <c r="J403" s="8" t="s">
         <v>2572</v>
       </c>
@@ -21741,12 +23020,27 @@
       <c r="B404" t="s">
         <v>695</v>
       </c>
+      <c r="C404" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D404" t="s">
+        <v>2649</v>
+      </c>
       <c r="E404" t="s">
         <v>679</v>
       </c>
       <c r="F404" t="s">
         <v>696</v>
       </c>
+      <c r="G404" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H404" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I404" t="s">
+        <v>2612</v>
+      </c>
       <c r="J404" t="s">
         <v>2572</v>
       </c>
@@ -21782,6 +23076,9 @@
       <c r="H405" t="s">
         <v>1855</v>
       </c>
+      <c r="I405" t="s">
+        <v>2626</v>
+      </c>
       <c r="J405" s="8" t="s">
         <v>2572</v>
       </c>
@@ -21823,6 +23120,9 @@
       <c r="H406" t="s">
         <v>1803</v>
       </c>
+      <c r="I406" t="s">
+        <v>2626</v>
+      </c>
       <c r="K406" s="8" t="s">
         <v>2562</v>
       </c>
@@ -21843,12 +23143,27 @@
       <c r="B407" t="s">
         <v>701</v>
       </c>
+      <c r="C407" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D407" t="s">
+        <v>2261</v>
+      </c>
       <c r="E407" t="s">
         <v>466</v>
       </c>
       <c r="F407" t="s">
         <v>702</v>
       </c>
+      <c r="G407" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H407" t="s">
+        <v>2656</v>
+      </c>
+      <c r="I407" t="s">
+        <v>2612</v>
+      </c>
       <c r="K407" t="s">
         <v>2548</v>
       </c>
@@ -21881,6 +23196,9 @@
       <c r="H408" t="s">
         <v>1400</v>
       </c>
+      <c r="I408" t="s">
+        <v>2626</v>
+      </c>
       <c r="K408" s="8" t="s">
         <v>2548</v>
       </c>
@@ -21916,6 +23234,9 @@
       <c r="G409" t="s">
         <v>1788</v>
       </c>
+      <c r="I409" t="s">
+        <v>2624</v>
+      </c>
       <c r="K409" t="s">
         <v>2565</v>
       </c>
@@ -21951,6 +23272,9 @@
       <c r="G410" t="s">
         <v>1788</v>
       </c>
+      <c r="I410" t="s">
+        <v>2613</v>
+      </c>
       <c r="K410" s="8" t="s">
         <v>2565</v>
       </c>
@@ -21986,6 +23310,9 @@
       <c r="G411" t="s">
         <v>1788</v>
       </c>
+      <c r="I411" t="s">
+        <v>2614</v>
+      </c>
       <c r="K411" s="8" t="s">
         <v>2565</v>
       </c>
@@ -22021,6 +23348,9 @@
       <c r="G412" t="s">
         <v>1788</v>
       </c>
+      <c r="I412" t="s">
+        <v>2613</v>
+      </c>
       <c r="K412" s="8" t="s">
         <v>2565</v>
       </c>
@@ -22056,6 +23386,9 @@
       <c r="G413" t="s">
         <v>1788</v>
       </c>
+      <c r="I413" t="s">
+        <v>2614</v>
+      </c>
       <c r="K413" s="8" t="s">
         <v>2565</v>
       </c>
@@ -22091,6 +23424,9 @@
       <c r="G414" t="s">
         <v>1788</v>
       </c>
+      <c r="I414" t="s">
+        <v>2624</v>
+      </c>
       <c r="K414" t="s">
         <v>2565</v>
       </c>
@@ -22126,6 +23462,9 @@
       <c r="G415" t="s">
         <v>1788</v>
       </c>
+      <c r="I415" t="s">
+        <v>2616</v>
+      </c>
       <c r="K415" s="8" t="s">
         <v>2565</v>
       </c>
@@ -22162,7 +23501,7 @@
         <v>1788</v>
       </c>
       <c r="I416" t="s">
-        <v>2633</v>
+        <v>2616</v>
       </c>
       <c r="K416" s="8" t="s">
         <v>2565</v>
@@ -22199,6 +23538,9 @@
       <c r="G417" t="s">
         <v>1788</v>
       </c>
+      <c r="I417" t="s">
+        <v>2616</v>
+      </c>
       <c r="K417" s="8" t="s">
         <v>2565</v>
       </c>
@@ -22234,6 +23576,9 @@
       <c r="G418" t="s">
         <v>1788</v>
       </c>
+      <c r="I418" t="s">
+        <v>2613</v>
+      </c>
       <c r="K418" s="8" t="s">
         <v>2565</v>
       </c>
@@ -22269,6 +23614,9 @@
       <c r="G419" t="s">
         <v>1788</v>
       </c>
+      <c r="I419" t="s">
+        <v>2616</v>
+      </c>
       <c r="K419" s="8" t="s">
         <v>2565</v>
       </c>
@@ -22304,6 +23652,9 @@
       <c r="G420" t="s">
         <v>1788</v>
       </c>
+      <c r="I420" t="s">
+        <v>2634</v>
+      </c>
       <c r="K420" t="s">
         <v>2565</v>
       </c>
@@ -22339,6 +23690,9 @@
       <c r="G421" t="s">
         <v>1788</v>
       </c>
+      <c r="I421" t="s">
+        <v>2614</v>
+      </c>
       <c r="K421" s="8" t="s">
         <v>2565</v>
       </c>
@@ -22374,6 +23728,9 @@
       <c r="G422" t="s">
         <v>1788</v>
       </c>
+      <c r="I422" t="s">
+        <v>2659</v>
+      </c>
       <c r="K422" s="8" t="s">
         <v>2565</v>
       </c>
@@ -22409,6 +23766,9 @@
       <c r="G423" t="s">
         <v>1788</v>
       </c>
+      <c r="I423" t="s">
+        <v>2625</v>
+      </c>
       <c r="K423" t="s">
         <v>2565</v>
       </c>
@@ -22444,6 +23804,9 @@
       <c r="G424" t="s">
         <v>1788</v>
       </c>
+      <c r="I424" t="s">
+        <v>2613</v>
+      </c>
       <c r="K424" s="8" t="s">
         <v>2565</v>
       </c>
@@ -22479,6 +23842,9 @@
       <c r="G425" t="s">
         <v>1788</v>
       </c>
+      <c r="I425" t="s">
+        <v>2612</v>
+      </c>
       <c r="K425" s="8" t="s">
         <v>2565</v>
       </c>
@@ -22514,6 +23880,9 @@
       <c r="G426" t="s">
         <v>1788</v>
       </c>
+      <c r="I426" t="s">
+        <v>2615</v>
+      </c>
       <c r="K426" t="s">
         <v>2565</v>
       </c>
@@ -22549,6 +23918,9 @@
       <c r="G427" t="s">
         <v>1788</v>
       </c>
+      <c r="I427" t="s">
+        <v>2615</v>
+      </c>
       <c r="K427" t="s">
         <v>2565</v>
       </c>
@@ -22584,6 +23956,9 @@
       <c r="G428" t="s">
         <v>1788</v>
       </c>
+      <c r="I428" t="s">
+        <v>2616</v>
+      </c>
       <c r="K428" s="8" t="s">
         <v>2565</v>
       </c>
@@ -22619,6 +23994,9 @@
       <c r="G429" t="s">
         <v>1788</v>
       </c>
+      <c r="I429" t="s">
+        <v>2625</v>
+      </c>
       <c r="K429" t="s">
         <v>2565</v>
       </c>
@@ -22654,6 +24032,9 @@
       <c r="G430" t="s">
         <v>1788</v>
       </c>
+      <c r="I430" t="s">
+        <v>2613</v>
+      </c>
       <c r="K430" s="8" t="s">
         <v>2565</v>
       </c>
@@ -22689,6 +24070,9 @@
       <c r="G431" t="s">
         <v>1788</v>
       </c>
+      <c r="I431" t="s">
+        <v>2616</v>
+      </c>
       <c r="K431" s="8" t="s">
         <v>2565</v>
       </c>
@@ -22724,6 +24108,9 @@
       <c r="G432" t="s">
         <v>1788</v>
       </c>
+      <c r="I432" t="s">
+        <v>2614</v>
+      </c>
       <c r="K432" s="8" t="s">
         <v>2565</v>
       </c>
@@ -22759,6 +24146,9 @@
       <c r="G433" t="s">
         <v>1788</v>
       </c>
+      <c r="I433" t="s">
+        <v>2625</v>
+      </c>
       <c r="K433" t="s">
         <v>2565</v>
       </c>
@@ -22794,6 +24184,9 @@
       <c r="G434" t="s">
         <v>1788</v>
       </c>
+      <c r="I434" t="s">
+        <v>2625</v>
+      </c>
       <c r="K434" t="s">
         <v>2565</v>
       </c>
@@ -22829,6 +24222,9 @@
       <c r="G435" t="s">
         <v>1788</v>
       </c>
+      <c r="I435" t="s">
+        <v>2614</v>
+      </c>
       <c r="K435" s="8" t="s">
         <v>2565</v>
       </c>
@@ -22864,6 +24260,9 @@
       <c r="G436" t="s">
         <v>1788</v>
       </c>
+      <c r="I436" t="s">
+        <v>2613</v>
+      </c>
       <c r="K436" s="8" t="s">
         <v>2565</v>
       </c>
@@ -22899,6 +24298,9 @@
       <c r="G437" t="s">
         <v>1788</v>
       </c>
+      <c r="I437" t="s">
+        <v>2616</v>
+      </c>
       <c r="K437" s="8" t="s">
         <v>2565</v>
       </c>
@@ -22934,6 +24336,9 @@
       <c r="G438" t="s">
         <v>1788</v>
       </c>
+      <c r="I438" t="s">
+        <v>2613</v>
+      </c>
       <c r="K438" s="8" t="s">
         <v>2565</v>
       </c>
@@ -22969,6 +24374,9 @@
       <c r="G439" t="s">
         <v>1788</v>
       </c>
+      <c r="I439" t="s">
+        <v>2613</v>
+      </c>
       <c r="K439" s="8" t="s">
         <v>2565</v>
       </c>
@@ -23004,6 +24412,9 @@
       <c r="G440" t="s">
         <v>1788</v>
       </c>
+      <c r="I440" t="s">
+        <v>2613</v>
+      </c>
       <c r="K440" s="8" t="s">
         <v>2565</v>
       </c>
@@ -23039,6 +24450,9 @@
       <c r="G441" t="s">
         <v>1788</v>
       </c>
+      <c r="I441" t="s">
+        <v>2616</v>
+      </c>
       <c r="K441" s="8" t="s">
         <v>2565</v>
       </c>
@@ -23074,6 +24488,9 @@
       <c r="G442" t="s">
         <v>1788</v>
       </c>
+      <c r="I442" t="s">
+        <v>2613</v>
+      </c>
       <c r="K442" s="8" t="s">
         <v>2565</v>
       </c>
@@ -23109,6 +24526,9 @@
       <c r="G443" t="s">
         <v>1788</v>
       </c>
+      <c r="I443" s="13" t="s">
+        <v>2625</v>
+      </c>
       <c r="K443" t="s">
         <v>2565</v>
       </c>
@@ -23144,6 +24564,9 @@
       <c r="G444" t="s">
         <v>1788</v>
       </c>
+      <c r="I444" t="s">
+        <v>2612</v>
+      </c>
       <c r="K444" s="8" t="s">
         <v>2565</v>
       </c>
@@ -23179,6 +24602,9 @@
       <c r="G445" t="s">
         <v>1788</v>
       </c>
+      <c r="I445" s="13" t="s">
+        <v>2625</v>
+      </c>
       <c r="K445" t="s">
         <v>2565</v>
       </c>
@@ -23214,6 +24640,9 @@
       <c r="G446" t="s">
         <v>1788</v>
       </c>
+      <c r="I446" t="s">
+        <v>2624</v>
+      </c>
       <c r="K446" t="s">
         <v>2565</v>
       </c>
@@ -23249,6 +24678,9 @@
       <c r="G447" t="s">
         <v>1788</v>
       </c>
+      <c r="I447" t="s">
+        <v>2615</v>
+      </c>
       <c r="K447" t="s">
         <v>2565</v>
       </c>
@@ -23284,6 +24716,9 @@
       <c r="G448" t="s">
         <v>1788</v>
       </c>
+      <c r="I448" t="s">
+        <v>2615</v>
+      </c>
       <c r="K448" t="s">
         <v>2565</v>
       </c>
@@ -23319,6 +24754,9 @@
       <c r="G449" t="s">
         <v>1788</v>
       </c>
+      <c r="I449" t="s">
+        <v>2633</v>
+      </c>
       <c r="K449" s="8" t="s">
         <v>2565</v>
       </c>
@@ -23619,6 +25057,12 @@
       <c r="B458" t="s">
         <v>770</v>
       </c>
+      <c r="C458" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D458" t="s">
+        <v>2650</v>
+      </c>
       <c r="E458" t="s">
         <v>133</v>
       </c>
@@ -23626,7 +25070,13 @@
         <v>771</v>
       </c>
       <c r="G458" t="s">
-        <v>1788</v>
+        <v>1801</v>
+      </c>
+      <c r="H458" t="s">
+        <v>1389</v>
+      </c>
+      <c r="I458" t="s">
+        <v>2613</v>
       </c>
       <c r="J458" t="s">
         <v>2555</v>
@@ -23646,12 +25096,27 @@
       <c r="B459" t="s">
         <v>772</v>
       </c>
+      <c r="C459" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D459" t="s">
+        <v>2650</v>
+      </c>
       <c r="E459" t="s">
         <v>133</v>
       </c>
       <c r="F459" t="s">
         <v>773</v>
       </c>
+      <c r="G459" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H459" t="s">
+        <v>1389</v>
+      </c>
+      <c r="I459" t="s">
+        <v>2613</v>
+      </c>
       <c r="J459" t="s">
         <v>2555</v>
       </c>
@@ -23669,12 +25134,27 @@
       <c r="B460" t="s">
         <v>774</v>
       </c>
+      <c r="C460" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D460" t="s">
+        <v>2650</v>
+      </c>
       <c r="E460" t="s">
         <v>133</v>
       </c>
       <c r="F460" t="s">
         <v>775</v>
       </c>
+      <c r="G460" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H460" t="s">
+        <v>1389</v>
+      </c>
+      <c r="I460" t="s">
+        <v>2613</v>
+      </c>
       <c r="J460" t="s">
         <v>2555</v>
       </c>
@@ -23692,12 +25172,27 @@
       <c r="B461" t="s">
         <v>776</v>
       </c>
+      <c r="C461" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D461" t="s">
+        <v>2650</v>
+      </c>
       <c r="E461" t="s">
         <v>133</v>
       </c>
       <c r="F461" t="s">
         <v>777</v>
       </c>
+      <c r="G461" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H461" t="s">
+        <v>1389</v>
+      </c>
+      <c r="I461" t="s">
+        <v>2613</v>
+      </c>
       <c r="J461" t="s">
         <v>2555</v>
       </c>
@@ -24170,12 +25665,27 @@
       <c r="B475" t="s">
         <v>806</v>
       </c>
+      <c r="C475" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D475" t="s">
+        <v>2651</v>
+      </c>
       <c r="E475" t="s">
         <v>104</v>
       </c>
       <c r="F475" t="s">
         <v>807</v>
       </c>
+      <c r="G475" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H475" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I475" t="s">
+        <v>2613</v>
+      </c>
       <c r="J475" t="s">
         <v>2584</v>
       </c>
@@ -24193,12 +25703,27 @@
       <c r="B476" t="s">
         <v>808</v>
       </c>
+      <c r="C476" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D476" t="s">
+        <v>2651</v>
+      </c>
       <c r="E476" t="s">
         <v>104</v>
       </c>
       <c r="F476" t="s">
         <v>809</v>
       </c>
+      <c r="G476" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H476" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I476" s="14" t="s">
+        <v>2613</v>
+      </c>
       <c r="J476" t="s">
         <v>2584</v>
       </c>
@@ -24216,12 +25741,27 @@
       <c r="B477" t="s">
         <v>810</v>
       </c>
+      <c r="C477" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D477" t="s">
+        <v>2651</v>
+      </c>
       <c r="E477" t="s">
         <v>104</v>
       </c>
       <c r="F477" t="s">
         <v>811</v>
       </c>
+      <c r="G477" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H477" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I477" s="14" t="s">
+        <v>2613</v>
+      </c>
       <c r="J477" t="s">
         <v>2584</v>
       </c>
@@ -24783,10 +26323,25 @@
       <c r="B495" t="s">
         <v>831</v>
       </c>
+      <c r="C495" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D495" t="s">
+        <v>2652</v>
+      </c>
       <c r="E495" t="s">
         <v>832</v>
       </c>
-      <c r="K495" s="8" t="s">
+      <c r="G495" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H495" t="s">
+        <v>2656</v>
+      </c>
+      <c r="I495" t="s">
+        <v>2613</v>
+      </c>
+      <c r="K495" t="s">
         <v>2548</v>
       </c>
       <c r="L495" s="7"/>
@@ -24817,7 +26372,7 @@
         <v>1390</v>
       </c>
       <c r="I496" t="s">
-        <v>2629</v>
+        <v>2627</v>
       </c>
       <c r="K496" s="8" t="s">
         <v>2599</v>
@@ -24852,7 +26407,7 @@
         <v>1390</v>
       </c>
       <c r="I497" t="s">
-        <v>2629</v>
+        <v>2627</v>
       </c>
       <c r="K497" s="8" t="s">
         <v>2599</v>
@@ -24887,7 +26442,7 @@
         <v>1390</v>
       </c>
       <c r="I498" t="s">
-        <v>2629</v>
+        <v>2627</v>
       </c>
       <c r="K498" s="8" t="s">
         <v>2599</v>
@@ -24922,7 +26477,7 @@
         <v>1390</v>
       </c>
       <c r="I499" t="s">
-        <v>2629</v>
+        <v>2627</v>
       </c>
       <c r="K499" s="8" t="s">
         <v>2599</v>
@@ -24957,7 +26512,7 @@
         <v>1390</v>
       </c>
       <c r="I500" t="s">
-        <v>2629</v>
+        <v>2627</v>
       </c>
       <c r="K500" s="8" t="s">
         <v>2599</v>
@@ -24992,7 +26547,7 @@
         <v>1390</v>
       </c>
       <c r="I501" t="s">
-        <v>2629</v>
+        <v>2627</v>
       </c>
       <c r="K501" s="8" t="s">
         <v>2599</v>
@@ -25027,7 +26582,7 @@
         <v>1390</v>
       </c>
       <c r="I502" t="s">
-        <v>2629</v>
+        <v>2627</v>
       </c>
       <c r="K502" s="8" t="s">
         <v>2599</v>
@@ -25062,7 +26617,7 @@
         <v>1390</v>
       </c>
       <c r="I503" t="s">
-        <v>2629</v>
+        <v>2627</v>
       </c>
       <c r="K503" s="8" t="s">
         <v>2599</v>
@@ -25097,7 +26652,7 @@
         <v>1390</v>
       </c>
       <c r="I504" t="s">
-        <v>2629</v>
+        <v>2627</v>
       </c>
       <c r="K504" s="8" t="s">
         <v>2599</v>
@@ -25132,7 +26687,7 @@
         <v>1390</v>
       </c>
       <c r="I505" t="s">
-        <v>2629</v>
+        <v>2627</v>
       </c>
       <c r="K505" s="8" t="s">
         <v>2599</v>
@@ -25167,7 +26722,7 @@
         <v>1390</v>
       </c>
       <c r="I506" t="s">
-        <v>2629</v>
+        <v>2627</v>
       </c>
       <c r="K506" s="8" t="s">
         <v>2599</v>
@@ -25202,7 +26757,7 @@
         <v>1390</v>
       </c>
       <c r="I507" t="s">
-        <v>2629</v>
+        <v>2627</v>
       </c>
       <c r="K507" s="8" t="s">
         <v>2599</v>
@@ -25237,7 +26792,7 @@
         <v>1390</v>
       </c>
       <c r="I508" t="s">
-        <v>2629</v>
+        <v>2627</v>
       </c>
       <c r="K508" s="8" t="s">
         <v>2599</v>
@@ -25272,7 +26827,7 @@
         <v>1390</v>
       </c>
       <c r="I509" t="s">
-        <v>2629</v>
+        <v>2627</v>
       </c>
       <c r="K509" s="8" t="s">
         <v>2599</v>
@@ -25307,7 +26862,7 @@
         <v>1390</v>
       </c>
       <c r="I510" t="s">
-        <v>2629</v>
+        <v>2627</v>
       </c>
       <c r="K510" s="8" t="s">
         <v>2599</v>
@@ -25342,7 +26897,7 @@
         <v>1390</v>
       </c>
       <c r="I511" t="s">
-        <v>2629</v>
+        <v>2627</v>
       </c>
       <c r="K511" s="8" t="s">
         <v>2599</v>
@@ -25377,7 +26932,7 @@
         <v>1390</v>
       </c>
       <c r="I512" t="s">
-        <v>2629</v>
+        <v>2627</v>
       </c>
       <c r="K512" s="8" t="s">
         <v>2599</v>
@@ -25396,11 +26951,26 @@
       <c r="B513" t="s">
         <v>850</v>
       </c>
+      <c r="C513" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D513" t="s">
+        <v>2269</v>
+      </c>
       <c r="E513" t="s">
         <v>536</v>
       </c>
       <c r="F513" t="s">
         <v>851</v>
+      </c>
+      <c r="G513" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H513" t="s">
+        <v>1394</v>
+      </c>
+      <c r="I513" s="14" t="s">
+        <v>2613</v>
       </c>
       <c r="J513" t="s">
         <v>2584</v>
@@ -25438,6 +27008,9 @@
       <c r="H514" t="s">
         <v>1389</v>
       </c>
+      <c r="I514" t="s">
+        <v>2624</v>
+      </c>
       <c r="J514" t="s">
         <v>2584</v>
       </c>
@@ -25461,12 +27034,27 @@
       <c r="B515" t="s">
         <v>854</v>
       </c>
+      <c r="C515" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D515" t="s">
+        <v>2269</v>
+      </c>
       <c r="E515" t="s">
         <v>536</v>
       </c>
       <c r="F515" t="s">
         <v>855</v>
       </c>
+      <c r="G515" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H515" t="s">
+        <v>1394</v>
+      </c>
+      <c r="I515" s="14" t="s">
+        <v>2613</v>
+      </c>
       <c r="J515" t="s">
         <v>2584</v>
       </c>
@@ -25502,6 +27090,9 @@
       <c r="H516" t="s">
         <v>1389</v>
       </c>
+      <c r="I516" t="s">
+        <v>2626</v>
+      </c>
       <c r="J516" t="s">
         <v>2584</v>
       </c>
@@ -25522,12 +27113,27 @@
       <c r="B517" t="s">
         <v>858</v>
       </c>
+      <c r="C517" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D517" t="s">
+        <v>2269</v>
+      </c>
       <c r="E517" t="s">
         <v>536</v>
       </c>
       <c r="F517" t="s">
         <v>859</v>
       </c>
+      <c r="G517" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H517" t="s">
+        <v>1394</v>
+      </c>
+      <c r="I517" s="14" t="s">
+        <v>2613</v>
+      </c>
       <c r="J517" t="s">
         <v>2584</v>
       </c>
@@ -25562,6 +27168,9 @@
       </c>
       <c r="H518" t="s">
         <v>1389</v>
+      </c>
+      <c r="I518" t="s">
+        <v>2624</v>
       </c>
       <c r="J518" t="s">
         <v>2584</v>
@@ -25587,7 +27196,7 @@
         <v>862</v>
       </c>
       <c r="O519" s="1" t="s">
-        <v>2634</v>
+        <v>2631</v>
       </c>
     </row>
     <row r="520" spans="1:15" ht="16" x14ac:dyDescent="0.2">
@@ -25717,9 +27326,6 @@
       <c r="H523" t="s">
         <v>2074</v>
       </c>
-      <c r="I523" t="s">
-        <v>2623</v>
-      </c>
       <c r="K523" t="s">
         <v>2602</v>
       </c>
@@ -25759,7 +27365,7 @@
         <v>2074</v>
       </c>
       <c r="I524" t="s">
-        <v>2626</v>
+        <v>2624</v>
       </c>
       <c r="K524" t="s">
         <v>2603</v>
@@ -25800,7 +27406,7 @@
         <v>2074</v>
       </c>
       <c r="I525" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="K525" t="s">
         <v>2603</v>
@@ -25841,7 +27447,7 @@
         <v>2074</v>
       </c>
       <c r="I526" t="s">
-        <v>2624</v>
+        <v>2622</v>
       </c>
       <c r="K526" t="s">
         <v>2603</v>
@@ -25875,11 +27481,23 @@
       <c r="B528" t="s">
         <v>880</v>
       </c>
+      <c r="C528" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D528" s="14" t="s">
+        <v>2271</v>
+      </c>
       <c r="E528" t="s">
         <v>871</v>
       </c>
       <c r="F528" t="s">
         <v>881</v>
+      </c>
+      <c r="G528" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H528" t="s">
+        <v>2074</v>
       </c>
       <c r="I528" t="s">
         <v>2613</v>
@@ -25918,7 +27536,7 @@
         <v>2074</v>
       </c>
       <c r="I529" t="s">
-        <v>2625</v>
+        <v>2623</v>
       </c>
       <c r="K529" t="s">
         <v>2602</v>
@@ -25959,7 +27577,7 @@
         <v>2074</v>
       </c>
       <c r="I530" t="s">
-        <v>2622</v>
+        <v>2621</v>
       </c>
       <c r="K530" t="s">
         <v>2603</v>
@@ -25993,11 +27611,23 @@
       <c r="B532" t="s">
         <v>887</v>
       </c>
+      <c r="C532" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D532" t="s">
+        <v>2271</v>
+      </c>
       <c r="E532" t="s">
         <v>871</v>
       </c>
       <c r="F532" t="s">
         <v>888</v>
+      </c>
+      <c r="G532" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H532" t="s">
+        <v>2074</v>
       </c>
       <c r="I532" t="s">
         <v>2613</v>
@@ -26036,7 +27666,7 @@
         <v>2074</v>
       </c>
       <c r="I533" t="s">
-        <v>2625</v>
+        <v>2623</v>
       </c>
       <c r="K533" t="s">
         <v>2602</v>
@@ -26058,11 +27688,23 @@
       <c r="B534" t="s">
         <v>891</v>
       </c>
+      <c r="C534" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D534" t="s">
+        <v>2271</v>
+      </c>
       <c r="E534" t="s">
         <v>871</v>
       </c>
       <c r="F534" t="s">
         <v>892</v>
+      </c>
+      <c r="G534" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H534" t="s">
+        <v>2074</v>
       </c>
       <c r="I534" t="s">
         <v>2613</v>
@@ -26101,7 +27743,7 @@
         <v>2074</v>
       </c>
       <c r="I535" t="s">
-        <v>2624</v>
+        <v>2622</v>
       </c>
       <c r="K535" t="s">
         <v>2603</v>
@@ -26135,11 +27777,23 @@
       <c r="B537" t="s">
         <v>896</v>
       </c>
+      <c r="C537" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D537" s="14" t="s">
+        <v>2271</v>
+      </c>
       <c r="E537" t="s">
         <v>871</v>
       </c>
       <c r="F537" t="s">
         <v>897</v>
+      </c>
+      <c r="G537" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H537" t="s">
+        <v>2074</v>
       </c>
       <c r="I537" t="s">
         <v>2613</v>
@@ -26178,7 +27832,7 @@
         <v>2074</v>
       </c>
       <c r="I538" t="s">
-        <v>2625</v>
+        <v>2623</v>
       </c>
       <c r="K538" t="s">
         <v>2602</v>
@@ -26219,7 +27873,7 @@
         <v>2074</v>
       </c>
       <c r="I539" t="s">
-        <v>2622</v>
+        <v>2621</v>
       </c>
       <c r="K539" t="s">
         <v>2603</v>
@@ -26256,6 +27910,9 @@
       <c r="G540" t="s">
         <v>1788</v>
       </c>
+      <c r="I540" t="s">
+        <v>2624</v>
+      </c>
       <c r="K540" t="s">
         <v>2565</v>
       </c>
@@ -26291,6 +27948,9 @@
       <c r="G541" t="s">
         <v>1788</v>
       </c>
+      <c r="I541" t="s">
+        <v>2613</v>
+      </c>
       <c r="K541" t="s">
         <v>2565</v>
       </c>
@@ -26326,6 +27986,9 @@
       <c r="G542" t="s">
         <v>1788</v>
       </c>
+      <c r="I542" t="s">
+        <v>2614</v>
+      </c>
       <c r="K542" t="s">
         <v>2565</v>
       </c>
@@ -26361,6 +28024,9 @@
       <c r="G543" t="s">
         <v>1788</v>
       </c>
+      <c r="I543" t="s">
+        <v>2613</v>
+      </c>
       <c r="K543" t="s">
         <v>2565</v>
       </c>
@@ -26396,6 +28062,9 @@
       <c r="G544" t="s">
         <v>1788</v>
       </c>
+      <c r="I544" t="s">
+        <v>2614</v>
+      </c>
       <c r="K544" t="s">
         <v>2565</v>
       </c>
@@ -26431,6 +28100,9 @@
       <c r="G545" t="s">
         <v>1788</v>
       </c>
+      <c r="I545" t="s">
+        <v>2624</v>
+      </c>
       <c r="K545" t="s">
         <v>2565</v>
       </c>
@@ -26466,6 +28138,9 @@
       <c r="G546" t="s">
         <v>1788</v>
       </c>
+      <c r="I546" s="13" t="s">
+        <v>2616</v>
+      </c>
       <c r="K546" t="s">
         <v>2565</v>
       </c>
@@ -26501,6 +28176,9 @@
       <c r="G547" t="s">
         <v>1788</v>
       </c>
+      <c r="I547" t="s">
+        <v>2616</v>
+      </c>
       <c r="K547" t="s">
         <v>2565</v>
       </c>
@@ -26536,6 +28214,9 @@
       <c r="G548" t="s">
         <v>1788</v>
       </c>
+      <c r="I548" t="s">
+        <v>2616</v>
+      </c>
       <c r="K548" t="s">
         <v>2565</v>
       </c>
@@ -26571,6 +28252,9 @@
       <c r="G549" t="s">
         <v>1788</v>
       </c>
+      <c r="I549" t="s">
+        <v>2613</v>
+      </c>
       <c r="K549" t="s">
         <v>2565</v>
       </c>
@@ -26606,6 +28290,9 @@
       <c r="G550" t="s">
         <v>1788</v>
       </c>
+      <c r="I550" t="s">
+        <v>2616</v>
+      </c>
       <c r="K550" t="s">
         <v>2565</v>
       </c>
@@ -26641,6 +28328,9 @@
       <c r="G551" t="s">
         <v>1788</v>
       </c>
+      <c r="I551" t="s">
+        <v>2634</v>
+      </c>
       <c r="K551" t="s">
         <v>2565</v>
       </c>
@@ -26676,6 +28366,9 @@
       <c r="G552" t="s">
         <v>1788</v>
       </c>
+      <c r="I552" t="s">
+        <v>2614</v>
+      </c>
       <c r="K552" t="s">
         <v>2565</v>
       </c>
@@ -26711,6 +28404,9 @@
       <c r="G553" t="s">
         <v>1788</v>
       </c>
+      <c r="I553" t="s">
+        <v>2616</v>
+      </c>
       <c r="K553" t="s">
         <v>2565</v>
       </c>
@@ -26746,6 +28442,9 @@
       <c r="G554" t="s">
         <v>1788</v>
       </c>
+      <c r="I554" t="s">
+        <v>2625</v>
+      </c>
       <c r="K554" t="s">
         <v>2565</v>
       </c>
@@ -26781,6 +28480,9 @@
       <c r="G555" t="s">
         <v>1788</v>
       </c>
+      <c r="I555" t="s">
+        <v>2613</v>
+      </c>
       <c r="K555" t="s">
         <v>2565</v>
       </c>
@@ -26816,6 +28518,9 @@
       <c r="G556" t="s">
         <v>1788</v>
       </c>
+      <c r="I556" t="s">
+        <v>2612</v>
+      </c>
       <c r="K556" t="s">
         <v>2565</v>
       </c>
@@ -26851,6 +28556,9 @@
       <c r="G557" t="s">
         <v>1788</v>
       </c>
+      <c r="I557" t="s">
+        <v>2615</v>
+      </c>
       <c r="K557" t="s">
         <v>2565</v>
       </c>
@@ -26886,6 +28594,9 @@
       <c r="G558" t="s">
         <v>1788</v>
       </c>
+      <c r="I558" t="s">
+        <v>2615</v>
+      </c>
       <c r="K558" t="s">
         <v>2565</v>
       </c>
@@ -26921,6 +28632,9 @@
       <c r="G559" t="s">
         <v>1788</v>
       </c>
+      <c r="I559" t="s">
+        <v>2616</v>
+      </c>
       <c r="K559" t="s">
         <v>2565</v>
       </c>
@@ -26956,6 +28670,9 @@
       <c r="G560" t="s">
         <v>1788</v>
       </c>
+      <c r="I560" t="s">
+        <v>2625</v>
+      </c>
       <c r="K560" t="s">
         <v>2565</v>
       </c>
@@ -26991,6 +28708,9 @@
       <c r="G561" t="s">
         <v>1788</v>
       </c>
+      <c r="I561" t="s">
+        <v>2613</v>
+      </c>
       <c r="K561" t="s">
         <v>2565</v>
       </c>
@@ -27026,6 +28746,9 @@
       <c r="G562" t="s">
         <v>1788</v>
       </c>
+      <c r="I562" t="s">
+        <v>2616</v>
+      </c>
       <c r="K562" t="s">
         <v>2565</v>
       </c>
@@ -27099,6 +28822,9 @@
       <c r="G564" t="s">
         <v>1788</v>
       </c>
+      <c r="I564" t="s">
+        <v>2614</v>
+      </c>
       <c r="K564" s="13" t="s">
         <v>2565</v>
       </c>
@@ -27134,6 +28860,9 @@
       <c r="G565" t="s">
         <v>1788</v>
       </c>
+      <c r="I565" s="13" t="s">
+        <v>2625</v>
+      </c>
       <c r="K565" s="13" t="s">
         <v>2565</v>
       </c>
@@ -27169,6 +28898,9 @@
       <c r="G566" t="s">
         <v>1788</v>
       </c>
+      <c r="I566" s="13" t="s">
+        <v>2625</v>
+      </c>
       <c r="K566" s="13" t="s">
         <v>2565</v>
       </c>
@@ -27204,6 +28936,9 @@
       <c r="G567" t="s">
         <v>1788</v>
       </c>
+      <c r="I567" t="s">
+        <v>2614</v>
+      </c>
       <c r="K567" s="13" t="s">
         <v>2565</v>
       </c>
@@ -27239,6 +28974,9 @@
       <c r="G568" t="s">
         <v>1788</v>
       </c>
+      <c r="I568" s="13" t="s">
+        <v>2613</v>
+      </c>
       <c r="K568" s="13" t="s">
         <v>2565</v>
       </c>
@@ -27274,6 +29012,9 @@
       <c r="G569" t="s">
         <v>1788</v>
       </c>
+      <c r="I569" s="13" t="s">
+        <v>2616</v>
+      </c>
       <c r="K569" s="13" t="s">
         <v>2565</v>
       </c>
@@ -27309,6 +29050,9 @@
       <c r="G570" t="s">
         <v>1788</v>
       </c>
+      <c r="I570" t="s">
+        <v>2613</v>
+      </c>
       <c r="K570" s="13" t="s">
         <v>2565</v>
       </c>
@@ -27382,6 +29126,9 @@
       <c r="G572" t="s">
         <v>1788</v>
       </c>
+      <c r="I572" s="13" t="s">
+        <v>2613</v>
+      </c>
       <c r="K572" s="13" t="s">
         <v>2565</v>
       </c>
@@ -27417,6 +29164,9 @@
       <c r="G573" t="s">
         <v>1788</v>
       </c>
+      <c r="I573" s="13" t="s">
+        <v>2613</v>
+      </c>
       <c r="K573" s="13" t="s">
         <v>2565</v>
       </c>
@@ -27452,6 +29202,9 @@
       <c r="G574" t="s">
         <v>1788</v>
       </c>
+      <c r="I574" t="s">
+        <v>2612</v>
+      </c>
       <c r="K574" s="13" t="s">
         <v>2565</v>
       </c>
@@ -27487,6 +29240,9 @@
       <c r="G575" t="s">
         <v>1788</v>
       </c>
+      <c r="I575" t="s">
+        <v>2613</v>
+      </c>
       <c r="K575" s="13" t="s">
         <v>2565</v>
       </c>
@@ -27560,6 +29316,9 @@
       <c r="G577" t="s">
         <v>1788</v>
       </c>
+      <c r="I577" s="13" t="s">
+        <v>2625</v>
+      </c>
       <c r="K577" s="13" t="s">
         <v>2565</v>
       </c>
@@ -27595,6 +29354,9 @@
       <c r="G578" t="s">
         <v>1788</v>
       </c>
+      <c r="I578" t="s">
+        <v>2612</v>
+      </c>
       <c r="K578" s="13" t="s">
         <v>2565</v>
       </c>
@@ -27630,6 +29392,9 @@
       <c r="G579" t="s">
         <v>1788</v>
       </c>
+      <c r="I579" s="13" t="s">
+        <v>2625</v>
+      </c>
       <c r="K579" s="13" t="s">
         <v>2565</v>
       </c>
@@ -27665,6 +29430,9 @@
       <c r="G580" t="s">
         <v>1788</v>
       </c>
+      <c r="I580" t="s">
+        <v>2624</v>
+      </c>
       <c r="K580" s="13" t="s">
         <v>2565</v>
       </c>
@@ -27700,6 +29468,9 @@
       <c r="G581" t="s">
         <v>1788</v>
       </c>
+      <c r="I581" s="13" t="s">
+        <v>2615</v>
+      </c>
       <c r="K581" s="13" t="s">
         <v>2565</v>
       </c>
@@ -27735,6 +29506,9 @@
       <c r="G582" t="s">
         <v>1788</v>
       </c>
+      <c r="I582" t="s">
+        <v>2615</v>
+      </c>
       <c r="K582" s="13" t="s">
         <v>2565</v>
       </c>
@@ -27769,6 +29543,9 @@
       </c>
       <c r="G583" t="s">
         <v>1788</v>
+      </c>
+      <c r="I583" t="s">
+        <v>2660</v>
       </c>
       <c r="K583" s="13" t="s">
         <v>2565</v>
@@ -27804,6 +29581,15 @@
       <c r="C585" t="s">
         <v>1350</v>
       </c>
+      <c r="D585" t="s">
+        <v>2653</v>
+      </c>
+      <c r="G585" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H585" t="s">
+        <v>2657</v>
+      </c>
       <c r="I585" t="s">
         <v>2617</v>
       </c>
@@ -27821,6 +29607,15 @@
       <c r="C586" t="s">
         <v>1350</v>
       </c>
+      <c r="D586" t="s">
+        <v>2653</v>
+      </c>
+      <c r="G586" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H586" t="s">
+        <v>2657</v>
+      </c>
       <c r="I586" t="s">
         <v>2617</v>
       </c>
@@ -27838,6 +29633,15 @@
       <c r="C587" t="s">
         <v>1350</v>
       </c>
+      <c r="D587" t="s">
+        <v>2653</v>
+      </c>
+      <c r="G587" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H587" t="s">
+        <v>2657</v>
+      </c>
       <c r="I587" t="s">
         <v>2617</v>
       </c>
@@ -27855,6 +29659,15 @@
       <c r="C588" t="s">
         <v>1350</v>
       </c>
+      <c r="D588" t="s">
+        <v>2653</v>
+      </c>
+      <c r="G588" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H588" t="s">
+        <v>2657</v>
+      </c>
       <c r="I588" t="s">
         <v>2617</v>
       </c>
@@ -27872,6 +29685,15 @@
       <c r="C589" t="s">
         <v>1350</v>
       </c>
+      <c r="D589" t="s">
+        <v>2653</v>
+      </c>
+      <c r="G589" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H589" t="s">
+        <v>2657</v>
+      </c>
       <c r="I589" t="s">
         <v>2617</v>
       </c>
@@ -27889,6 +29711,15 @@
       <c r="C590" t="s">
         <v>1350</v>
       </c>
+      <c r="D590" t="s">
+        <v>2653</v>
+      </c>
+      <c r="G590" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H590" t="s">
+        <v>2657</v>
+      </c>
       <c r="I590" t="s">
         <v>2617</v>
       </c>
@@ -27906,6 +29737,15 @@
       <c r="C591" t="s">
         <v>1350</v>
       </c>
+      <c r="D591" t="s">
+        <v>2653</v>
+      </c>
+      <c r="G591" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H591" t="s">
+        <v>2657</v>
+      </c>
       <c r="I591" t="s">
         <v>2617</v>
       </c>
@@ -27986,9 +29826,21 @@
       <c r="B598" t="s">
         <v>969</v>
       </c>
+      <c r="C598" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D598" t="s">
+        <v>2654</v>
+      </c>
       <c r="E598" t="s">
         <v>2278</v>
       </c>
+      <c r="G598" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H598" t="s">
+        <v>2656</v>
+      </c>
       <c r="K598" t="s">
         <v>2548</v>
       </c>
@@ -28172,6 +30024,9 @@
       </c>
       <c r="H603" t="s">
         <v>2098</v>
+      </c>
+      <c r="I603" t="s">
+        <v>2624</v>
       </c>
       <c r="K603" s="8" t="s">
         <v>2604</v>
@@ -28982,7 +30837,7 @@
         <v>1402</v>
       </c>
       <c r="I632" t="s">
-        <v>2627</v>
+        <v>2625</v>
       </c>
       <c r="K632" s="8" t="s">
         <v>2605</v>
@@ -29026,11 +30881,11 @@
       <c r="C635" t="s">
         <v>1350</v>
       </c>
+      <c r="D635" t="s">
+        <v>2655</v>
+      </c>
       <c r="E635" t="s">
         <v>1023</v>
-      </c>
-      <c r="I635" t="s">
-        <v>2619</v>
       </c>
       <c r="O635" s="1" t="s">
         <v>1717</v>
@@ -29072,10 +30927,10 @@
         <v>2285</v>
       </c>
       <c r="G638" t="s">
-        <v>1402</v>
+        <v>2207</v>
       </c>
       <c r="I638" t="s">
-        <v>2620</v>
+        <v>2619</v>
       </c>
       <c r="K638" t="s">
         <v>2605</v>
@@ -29101,7 +30956,7 @@
         <v>2286</v>
       </c>
       <c r="G639" t="s">
-        <v>1402</v>
+        <v>2207</v>
       </c>
       <c r="I639" t="s">
         <v>2615</v>
@@ -29149,6 +31004,9 @@
       <c r="H641" t="s">
         <v>1855</v>
       </c>
+      <c r="I641" t="s">
+        <v>2624</v>
+      </c>
       <c r="K641" s="8" t="s">
         <v>2567</v>
       </c>
@@ -29180,7 +31038,13 @@
       <c r="B643" t="s">
         <v>1033</v>
       </c>
-      <c r="K643" s="8" t="s">
+      <c r="C643" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D643" t="s">
+        <v>2661</v>
+      </c>
+      <c r="K643" t="s">
         <v>2606</v>
       </c>
       <c r="O643" s="1" t="s">
@@ -29209,7 +31073,7 @@
         <v>2165</v>
       </c>
     </row>
-    <row r="646" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A646" t="s">
         <v>626</v>
       </c>
@@ -29220,7 +31084,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="647" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A647" t="s">
         <v>626</v>
       </c>
@@ -29231,7 +31095,7 @@
         <v>2303</v>
       </c>
     </row>
-    <row r="648" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A648" t="s">
         <v>626</v>
       </c>
@@ -29242,7 +31106,7 @@
         <v>2304</v>
       </c>
     </row>
-    <row r="649" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A649" t="s">
         <v>626</v>
       </c>
@@ -29253,7 +31117,7 @@
         <v>2305</v>
       </c>
     </row>
-    <row r="650" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A650" t="s">
         <v>626</v>
       </c>
@@ -29264,7 +31128,7 @@
         <v>2306</v>
       </c>
     </row>
-    <row r="651" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A651" t="s">
         <v>626</v>
       </c>
@@ -29275,7 +31139,7 @@
         <v>2307</v>
       </c>
     </row>
-    <row r="652" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A652" t="s">
         <v>626</v>
       </c>
@@ -29286,7 +31150,7 @@
         <v>2308</v>
       </c>
     </row>
-    <row r="653" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A653" t="s">
         <v>626</v>
       </c>
@@ -29297,7 +31161,7 @@
         <v>2309</v>
       </c>
     </row>
-    <row r="654" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A654" t="s">
         <v>626</v>
       </c>
@@ -29308,7 +31172,7 @@
         <v>2310</v>
       </c>
     </row>
-    <row r="655" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A655" t="s">
         <v>626</v>
       </c>
@@ -29319,7 +31183,7 @@
         <v>2311</v>
       </c>
     </row>
-    <row r="656" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A656" t="s">
         <v>626</v>
       </c>
@@ -29330,7 +31194,7 @@
         <v>2312</v>
       </c>
     </row>
-    <row r="657" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A657" t="s">
         <v>626</v>
       </c>
@@ -29341,7 +31205,7 @@
         <v>2313</v>
       </c>
     </row>
-    <row r="658" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A658" t="s">
         <v>626</v>
       </c>
@@ -29352,7 +31216,7 @@
         <v>2314</v>
       </c>
     </row>
-    <row r="659" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A659" t="s">
         <v>626</v>
       </c>
@@ -29363,7 +31227,7 @@
         <v>2315</v>
       </c>
     </row>
-    <row r="660" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A660" t="s">
         <v>626</v>
       </c>
@@ -29374,7 +31238,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="661" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A661" t="s">
         <v>626</v>
       </c>
@@ -29385,7 +31249,7 @@
         <v>2317</v>
       </c>
     </row>
-    <row r="662" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A662" t="s">
         <v>626</v>
       </c>
@@ -29396,7 +31260,7 @@
         <v>2318</v>
       </c>
     </row>
-    <row r="663" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A663" t="s">
         <v>626</v>
       </c>
@@ -29407,7 +31271,7 @@
         <v>2319</v>
       </c>
     </row>
-    <row r="664" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A664" t="s">
         <v>626</v>
       </c>
@@ -29418,7 +31282,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="665" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A665" t="s">
         <v>626</v>
       </c>
@@ -29429,7 +31293,7 @@
         <v>2321</v>
       </c>
     </row>
-    <row r="666" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A666" t="s">
         <v>626</v>
       </c>
@@ -29440,7 +31304,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="667" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A667" t="s">
         <v>626</v>
       </c>
@@ -29451,7 +31315,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="668" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A668" t="s">
         <v>626</v>
       </c>
@@ -29462,7 +31326,7 @@
         <v>2324</v>
       </c>
     </row>
-    <row r="669" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A669" t="s">
         <v>626</v>
       </c>
@@ -29473,7 +31337,7 @@
         <v>2325</v>
       </c>
     </row>
-    <row r="670" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A670" t="s">
         <v>626</v>
       </c>
@@ -29484,7 +31348,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="671" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A671" t="s">
         <v>626</v>
       </c>
@@ -29495,7 +31359,7 @@
         <v>2327</v>
       </c>
     </row>
-    <row r="672" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A672" t="s">
         <v>626</v>
       </c>
@@ -29506,7 +31370,7 @@
         <v>2328</v>
       </c>
     </row>
-    <row r="673" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A673" t="s">
         <v>626</v>
       </c>
@@ -29517,7 +31381,7 @@
         <v>2329</v>
       </c>
     </row>
-    <row r="674" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A674" t="s">
         <v>626</v>
       </c>
@@ -29528,7 +31392,7 @@
         <v>2330</v>
       </c>
     </row>
-    <row r="675" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A675" t="s">
         <v>626</v>
       </c>
@@ -29539,7 +31403,7 @@
         <v>2331</v>
       </c>
     </row>
-    <row r="676" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A676" t="s">
         <v>626</v>
       </c>
@@ -29550,7 +31414,7 @@
         <v>2332</v>
       </c>
     </row>
-    <row r="677" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A677" t="s">
         <v>626</v>
       </c>
@@ -29561,7 +31425,7 @@
         <v>2333</v>
       </c>
     </row>
-    <row r="678" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A678" t="s">
         <v>626</v>
       </c>
@@ -29572,7 +31436,7 @@
         <v>2334</v>
       </c>
     </row>
-    <row r="679" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A679" t="s">
         <v>626</v>
       </c>
@@ -29583,7 +31447,7 @@
         <v>2335</v>
       </c>
     </row>
-    <row r="680" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A680" t="s">
         <v>626</v>
       </c>
@@ -29594,7 +31458,7 @@
         <v>2336</v>
       </c>
     </row>
-    <row r="681" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A681" t="s">
         <v>626</v>
       </c>
@@ -29605,7 +31469,7 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="682" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A682" t="s">
         <v>626</v>
       </c>
@@ -29616,7 +31480,7 @@
         <v>2338</v>
       </c>
     </row>
-    <row r="683" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A683" t="s">
         <v>626</v>
       </c>
@@ -29627,7 +31491,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="684" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A684" t="s">
         <v>626</v>
       </c>
@@ -29638,7 +31502,7 @@
         <v>2340</v>
       </c>
     </row>
-    <row r="685" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A685" t="s">
         <v>626</v>
       </c>
@@ -29649,7 +31513,7 @@
         <v>2341</v>
       </c>
     </row>
-    <row r="686" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A686" t="s">
         <v>626</v>
       </c>
@@ -29660,7 +31524,7 @@
         <v>2342</v>
       </c>
     </row>
-    <row r="687" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A687" t="s">
         <v>626</v>
       </c>
@@ -29671,7 +31535,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="688" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A688" t="s">
         <v>626</v>
       </c>
@@ -29682,7 +31546,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="689" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A689" t="s">
         <v>626</v>
       </c>
@@ -29693,7 +31557,7 @@
         <v>2345</v>
       </c>
     </row>
-    <row r="690" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A690" t="s">
         <v>626</v>
       </c>
@@ -29704,7 +31568,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="691" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A691" t="s">
         <v>626</v>
       </c>
@@ -29715,7 +31579,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="692" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A692" t="s">
         <v>626</v>
       </c>
@@ -29726,7 +31590,7 @@
         <v>2348</v>
       </c>
     </row>
-    <row r="693" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A693" t="s">
         <v>626</v>
       </c>
@@ -29737,7 +31601,7 @@
         <v>2349</v>
       </c>
     </row>
-    <row r="694" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A694" t="s">
         <v>626</v>
       </c>
@@ -29748,7 +31612,7 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="695" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A695" t="s">
         <v>626</v>
       </c>
@@ -29759,7 +31623,7 @@
         <v>2351</v>
       </c>
     </row>
-    <row r="696" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A696" t="s">
         <v>626</v>
       </c>
@@ -29770,7 +31634,7 @@
         <v>2352</v>
       </c>
     </row>
-    <row r="697" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A697" t="s">
         <v>626</v>
       </c>
@@ -29781,7 +31645,7 @@
         <v>2353</v>
       </c>
     </row>
-    <row r="698" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A698" t="s">
         <v>626</v>
       </c>
@@ -29792,7 +31656,7 @@
         <v>2354</v>
       </c>
     </row>
-    <row r="699" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A699" t="s">
         <v>626</v>
       </c>
@@ -29803,7 +31667,7 @@
         <v>2355</v>
       </c>
     </row>
-    <row r="700" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A700" t="s">
         <v>626</v>
       </c>
@@ -29814,7 +31678,7 @@
         <v>2356</v>
       </c>
     </row>
-    <row r="701" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A701" t="s">
         <v>626</v>
       </c>
@@ -29825,7 +31689,7 @@
         <v>2357</v>
       </c>
     </row>
-    <row r="702" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A702" t="s">
         <v>626</v>
       </c>
@@ -29836,7 +31700,7 @@
         <v>2358</v>
       </c>
     </row>
-    <row r="703" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A703" t="s">
         <v>626</v>
       </c>
@@ -29847,7 +31711,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="704" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A704" t="s">
         <v>626</v>
       </c>
@@ -29858,7 +31722,7 @@
         <v>2360</v>
       </c>
     </row>
-    <row r="705" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A705" t="s">
         <v>626</v>
       </c>
@@ -29869,7 +31733,7 @@
         <v>2361</v>
       </c>
     </row>
-    <row r="706" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A706" t="s">
         <v>626</v>
       </c>
@@ -29880,7 +31744,7 @@
         <v>2362</v>
       </c>
     </row>
-    <row r="707" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A707" t="s">
         <v>626</v>
       </c>
@@ -29891,7 +31755,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="708" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A708" t="s">
         <v>626</v>
       </c>
@@ -29902,7 +31766,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="709" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A709" t="s">
         <v>626</v>
       </c>
@@ -29913,7 +31777,7 @@
         <v>2365</v>
       </c>
     </row>
-    <row r="710" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A710" t="s">
         <v>626</v>
       </c>
@@ -29924,7 +31788,7 @@
         <v>2366</v>
       </c>
     </row>
-    <row r="711" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A711" t="s">
         <v>626</v>
       </c>
@@ -29935,7 +31799,7 @@
         <v>2367</v>
       </c>
     </row>
-    <row r="712" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A712" t="s">
         <v>626</v>
       </c>
@@ -29946,7 +31810,7 @@
         <v>2368</v>
       </c>
     </row>
-    <row r="713" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A713" t="s">
         <v>626</v>
       </c>
@@ -29957,7 +31821,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="714" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A714" t="s">
         <v>626</v>
       </c>
@@ -29968,7 +31832,7 @@
         <v>2370</v>
       </c>
     </row>
-    <row r="715" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A715" t="s">
         <v>626</v>
       </c>
@@ -29979,7 +31843,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="716" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A716" t="s">
         <v>626</v>
       </c>
@@ -29990,7 +31854,7 @@
         <v>2372</v>
       </c>
     </row>
-    <row r="717" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A717" t="s">
         <v>626</v>
       </c>
@@ -30001,7 +31865,7 @@
         <v>2373</v>
       </c>
     </row>
-    <row r="718" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A718" t="s">
         <v>626</v>
       </c>
@@ -30012,7 +31876,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="719" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A719" t="s">
         <v>626</v>
       </c>
@@ -30023,7 +31887,7 @@
         <v>2375</v>
       </c>
     </row>
-    <row r="720" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A720" t="s">
         <v>626</v>
       </c>
@@ -30034,7 +31898,7 @@
         <v>2376</v>
       </c>
     </row>
-    <row r="721" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A721" t="s">
         <v>626</v>
       </c>
@@ -30045,7 +31909,7 @@
         <v>2377</v>
       </c>
     </row>
-    <row r="722" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A722" t="s">
         <v>626</v>
       </c>
@@ -30056,7 +31920,7 @@
         <v>2378</v>
       </c>
     </row>
-    <row r="723" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A723" t="s">
         <v>626</v>
       </c>
@@ -30067,7 +31931,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="724" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A724" t="s">
         <v>626</v>
       </c>
@@ -30078,7 +31942,7 @@
         <v>2380</v>
       </c>
     </row>
-    <row r="725" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A725" t="s">
         <v>626</v>
       </c>
@@ -30089,7 +31953,7 @@
         <v>2381</v>
       </c>
     </row>
-    <row r="726" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A726" t="s">
         <v>626</v>
       </c>
@@ -30100,7 +31964,7 @@
         <v>2382</v>
       </c>
     </row>
-    <row r="727" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A727" t="s">
         <v>626</v>
       </c>
@@ -30111,7 +31975,7 @@
         <v>2383</v>
       </c>
     </row>
-    <row r="728" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A728" t="s">
         <v>626</v>
       </c>
@@ -30122,7 +31986,7 @@
         <v>2384</v>
       </c>
     </row>
-    <row r="729" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A729" t="s">
         <v>626</v>
       </c>
@@ -30133,7 +31997,7 @@
         <v>2385</v>
       </c>
     </row>
-    <row r="730" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A730" t="s">
         <v>626</v>
       </c>
@@ -30144,7 +32008,7 @@
         <v>2386</v>
       </c>
     </row>
-    <row r="731" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A731" t="s">
         <v>626</v>
       </c>
@@ -30155,7 +32019,7 @@
         <v>2387</v>
       </c>
     </row>
-    <row r="732" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A732" t="s">
         <v>626</v>
       </c>
@@ -30166,7 +32030,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="733" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A733" t="s">
         <v>626</v>
       </c>
@@ -30177,7 +32041,7 @@
         <v>2389</v>
       </c>
     </row>
-    <row r="734" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A734" t="s">
         <v>626</v>
       </c>
@@ -30188,7 +32052,7 @@
         <v>2390</v>
       </c>
     </row>
-    <row r="735" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A735" t="s">
         <v>626</v>
       </c>
@@ -30199,7 +32063,7 @@
         <v>2391</v>
       </c>
     </row>
-    <row r="736" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A736" t="s">
         <v>626</v>
       </c>
@@ -30210,7 +32074,7 @@
         <v>2392</v>
       </c>
     </row>
-    <row r="737" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A737" t="s">
         <v>626</v>
       </c>
@@ -30221,7 +32085,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="738" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A738" t="s">
         <v>626</v>
       </c>
@@ -30232,7 +32096,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="739" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A739" t="s">
         <v>626</v>
       </c>
@@ -30243,7 +32107,7 @@
         <v>2395</v>
       </c>
     </row>
-    <row r="740" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A740" t="s">
         <v>626</v>
       </c>
@@ -30254,7 +32118,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="741" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A741" t="s">
         <v>626</v>
       </c>
@@ -30265,7 +32129,7 @@
         <v>2397</v>
       </c>
     </row>
-    <row r="742" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A742" t="s">
         <v>626</v>
       </c>
@@ -30276,7 +32140,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="743" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A743" t="s">
         <v>626</v>
       </c>
@@ -30287,7 +32151,7 @@
         <v>2399</v>
       </c>
     </row>
-    <row r="744" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A744" t="s">
         <v>626</v>
       </c>
@@ -30298,7 +32162,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="745" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A745" t="s">
         <v>626</v>
       </c>
@@ -30309,7 +32173,7 @@
         <v>2401</v>
       </c>
     </row>
-    <row r="746" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A746" t="s">
         <v>626</v>
       </c>
@@ -30320,7 +32184,7 @@
         <v>2402</v>
       </c>
     </row>
-    <row r="747" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A747" t="s">
         <v>626</v>
       </c>
@@ -30331,7 +32195,7 @@
         <v>2403</v>
       </c>
     </row>
-    <row r="748" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A748" t="s">
         <v>626</v>
       </c>
@@ -30342,7 +32206,7 @@
         <v>2404</v>
       </c>
     </row>
-    <row r="749" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A749" t="s">
         <v>626</v>
       </c>
@@ -30353,7 +32217,7 @@
         <v>2405</v>
       </c>
     </row>
-    <row r="750" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A750" t="s">
         <v>626</v>
       </c>
@@ -30364,7 +32228,7 @@
         <v>2406</v>
       </c>
     </row>
-    <row r="751" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A751" t="s">
         <v>626</v>
       </c>
@@ -30375,7 +32239,7 @@
         <v>2407</v>
       </c>
     </row>
-    <row r="752" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A752" t="s">
         <v>626</v>
       </c>
@@ -30386,7 +32250,7 @@
         <v>2408</v>
       </c>
     </row>
-    <row r="753" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A753" t="s">
         <v>626</v>
       </c>
@@ -30397,7 +32261,7 @@
         <v>2409</v>
       </c>
     </row>
-    <row r="754" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A754" t="s">
         <v>626</v>
       </c>
@@ -30408,7 +32272,7 @@
         <v>2410</v>
       </c>
     </row>
-    <row r="755" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A755" t="s">
         <v>626</v>
       </c>
@@ -30419,7 +32283,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="756" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A756" t="s">
         <v>626</v>
       </c>
@@ -30430,7 +32294,7 @@
         <v>2412</v>
       </c>
     </row>
-    <row r="757" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A757" t="s">
         <v>626</v>
       </c>
@@ -30441,7 +32305,7 @@
         <v>2413</v>
       </c>
     </row>
-    <row r="758" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A758" t="s">
         <v>626</v>
       </c>
@@ -30452,7 +32316,7 @@
         <v>2414</v>
       </c>
     </row>
-    <row r="759" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A759" t="s">
         <v>626</v>
       </c>
@@ -30463,7 +32327,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="760" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A760" t="s">
         <v>626</v>
       </c>
@@ -30474,7 +32338,7 @@
         <v>2416</v>
       </c>
     </row>
-    <row r="761" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A761" t="s">
         <v>626</v>
       </c>
@@ -30485,7 +32349,7 @@
         <v>2417</v>
       </c>
     </row>
-    <row r="762" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A762" t="s">
         <v>626</v>
       </c>
@@ -30496,7 +32360,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="763" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A763" t="s">
         <v>626</v>
       </c>
@@ -30507,7 +32371,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="764" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A764" t="s">
         <v>626</v>
       </c>
@@ -30518,7 +32382,7 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="765" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A765" t="s">
         <v>626</v>
       </c>
@@ -30529,7 +32393,7 @@
         <v>2421</v>
       </c>
     </row>
-    <row r="766" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A766" t="s">
         <v>626</v>
       </c>
@@ -30540,7 +32404,7 @@
         <v>2422</v>
       </c>
     </row>
-    <row r="767" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A767" t="s">
         <v>626</v>
       </c>
@@ -30551,7 +32415,7 @@
         <v>2423</v>
       </c>
     </row>
-    <row r="768" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A768" t="s">
         <v>626</v>
       </c>
@@ -30562,7 +32426,7 @@
         <v>2424</v>
       </c>
     </row>
-    <row r="769" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A769" t="s">
         <v>626</v>
       </c>
@@ -30573,7 +32437,7 @@
         <v>2425</v>
       </c>
     </row>
-    <row r="770" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A770" t="s">
         <v>626</v>
       </c>
@@ -30584,7 +32448,7 @@
         <v>2426</v>
       </c>
     </row>
-    <row r="771" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A771" t="s">
         <v>626</v>
       </c>
@@ -30595,7 +32459,7 @@
         <v>2427</v>
       </c>
     </row>
-    <row r="772" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A772" t="s">
         <v>626</v>
       </c>
@@ -30606,7 +32470,7 @@
         <v>2428</v>
       </c>
     </row>
-    <row r="773" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A773" t="s">
         <v>626</v>
       </c>
@@ -30617,7 +32481,7 @@
         <v>2429</v>
       </c>
     </row>
-    <row r="774" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A774" t="s">
         <v>626</v>
       </c>
@@ -30628,7 +32492,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="775" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A775" t="s">
         <v>626</v>
       </c>
@@ -30639,7 +32503,7 @@
         <v>2431</v>
       </c>
     </row>
-    <row r="776" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A776" t="s">
         <v>626</v>
       </c>
@@ -30650,7 +32514,7 @@
         <v>2432</v>
       </c>
     </row>
-    <row r="777" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A777" t="s">
         <v>626</v>
       </c>
@@ -30661,7 +32525,7 @@
         <v>2433</v>
       </c>
     </row>
-    <row r="778" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A778" t="s">
         <v>626</v>
       </c>
@@ -30672,7 +32536,7 @@
         <v>2434</v>
       </c>
     </row>
-    <row r="779" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A779" t="s">
         <v>626</v>
       </c>
@@ -30683,7 +32547,7 @@
         <v>2435</v>
       </c>
     </row>
-    <row r="780" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A780" t="s">
         <v>626</v>
       </c>
@@ -30694,7 +32558,7 @@
         <v>2436</v>
       </c>
     </row>
-    <row r="781" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A781" t="s">
         <v>626</v>
       </c>
@@ -30705,7 +32569,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="782" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A782" t="s">
         <v>626</v>
       </c>
@@ -30716,7 +32580,7 @@
         <v>2438</v>
       </c>
     </row>
-    <row r="783" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A783" t="s">
         <v>626</v>
       </c>
@@ -30727,7 +32591,7 @@
         <v>2439</v>
       </c>
     </row>
-    <row r="784" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A784" t="s">
         <v>626</v>
       </c>
@@ -30738,7 +32602,7 @@
         <v>2440</v>
       </c>
     </row>
-    <row r="785" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A785" t="s">
         <v>626</v>
       </c>
@@ -30749,7 +32613,7 @@
         <v>2441</v>
       </c>
     </row>
-    <row r="786" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A786" t="s">
         <v>626</v>
       </c>
@@ -30760,7 +32624,7 @@
         <v>2442</v>
       </c>
     </row>
-    <row r="787" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A787" t="s">
         <v>626</v>
       </c>
@@ -30771,7 +32635,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="788" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A788" t="s">
         <v>626</v>
       </c>
@@ -30782,7 +32646,7 @@
         <v>2444</v>
       </c>
     </row>
-    <row r="789" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A789" t="s">
         <v>626</v>
       </c>
@@ -30793,7 +32657,7 @@
         <v>2445</v>
       </c>
     </row>
-    <row r="790" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A790" t="s">
         <v>626</v>
       </c>
@@ -30804,7 +32668,7 @@
         <v>2446</v>
       </c>
     </row>
-    <row r="791" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A791" t="s">
         <v>626</v>
       </c>
@@ -30815,7 +32679,7 @@
         <v>2447</v>
       </c>
     </row>
-    <row r="792" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A792" t="s">
         <v>626</v>
       </c>
@@ -30826,7 +32690,7 @@
         <v>2448</v>
       </c>
     </row>
-    <row r="793" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A793" t="s">
         <v>626</v>
       </c>
@@ -30837,7 +32701,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="794" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A794" t="s">
         <v>626</v>
       </c>
@@ -30848,7 +32712,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="795" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A795" t="s">
         <v>626</v>
       </c>
@@ -30859,7 +32723,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="796" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A796" t="s">
         <v>626</v>
       </c>
@@ -30870,7 +32734,7 @@
         <v>2452</v>
       </c>
     </row>
-    <row r="797" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A797" t="s">
         <v>626</v>
       </c>
@@ -30881,7 +32745,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="798" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A798" t="s">
         <v>626</v>
       </c>
@@ -30892,7 +32756,7 @@
         <v>2454</v>
       </c>
     </row>
-    <row r="799" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A799" t="s">
         <v>626</v>
       </c>
@@ -30903,7 +32767,7 @@
         <v>2455</v>
       </c>
     </row>
-    <row r="800" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A800" t="s">
         <v>626</v>
       </c>
@@ -30914,7 +32778,7 @@
         <v>2456</v>
       </c>
     </row>
-    <row r="801" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A801" t="s">
         <v>626</v>
       </c>
@@ -30925,7 +32789,7 @@
         <v>2457</v>
       </c>
     </row>
-    <row r="802" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A802" t="s">
         <v>626</v>
       </c>
@@ -30936,7 +32800,7 @@
         <v>2458</v>
       </c>
     </row>
-    <row r="803" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A803" t="s">
         <v>626</v>
       </c>
@@ -30947,7 +32811,7 @@
         <v>2459</v>
       </c>
     </row>
-    <row r="804" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A804" t="s">
         <v>626</v>
       </c>
@@ -30958,7 +32822,7 @@
         <v>2460</v>
       </c>
     </row>
-    <row r="805" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A805" t="s">
         <v>626</v>
       </c>
@@ -30969,7 +32833,7 @@
         <v>2461</v>
       </c>
     </row>
-    <row r="806" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A806" t="s">
         <v>626</v>
       </c>
@@ -30980,7 +32844,7 @@
         <v>2462</v>
       </c>
     </row>
-    <row r="807" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A807" t="s">
         <v>626</v>
       </c>
@@ -30991,7 +32855,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="808" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A808" t="s">
         <v>626</v>
       </c>
@@ -31002,7 +32866,7 @@
         <v>2464</v>
       </c>
     </row>
-    <row r="809" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A809" t="s">
         <v>626</v>
       </c>
@@ -31013,7 +32877,7 @@
         <v>2465</v>
       </c>
     </row>
-    <row r="810" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A810" t="s">
         <v>626</v>
       </c>
@@ -31024,7 +32888,7 @@
         <v>2466</v>
       </c>
     </row>
-    <row r="811" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A811" t="s">
         <v>626</v>
       </c>
@@ -31035,7 +32899,7 @@
         <v>2467</v>
       </c>
     </row>
-    <row r="812" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A812" t="s">
         <v>626</v>
       </c>
@@ -31046,7 +32910,7 @@
         <v>2468</v>
       </c>
     </row>
-    <row r="813" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A813" t="s">
         <v>626</v>
       </c>
@@ -31057,7 +32921,7 @@
         <v>2469</v>
       </c>
     </row>
-    <row r="814" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A814" t="s">
         <v>626</v>
       </c>
@@ -31068,7 +32932,7 @@
         <v>2470</v>
       </c>
     </row>
-    <row r="815" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A815" t="s">
         <v>626</v>
       </c>
@@ -31079,7 +32943,7 @@
         <v>2471</v>
       </c>
     </row>
-    <row r="816" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A816" t="s">
         <v>626</v>
       </c>
@@ -31090,7 +32954,7 @@
         <v>2472</v>
       </c>
     </row>
-    <row r="817" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A817" t="s">
         <v>626</v>
       </c>
@@ -31101,7 +32965,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="818" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A818" t="s">
         <v>626</v>
       </c>
@@ -31112,7 +32976,7 @@
         <v>2474</v>
       </c>
     </row>
-    <row r="819" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A819" t="s">
         <v>626</v>
       </c>
@@ -31123,7 +32987,7 @@
         <v>2475</v>
       </c>
     </row>
-    <row r="820" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A820" t="s">
         <v>626</v>
       </c>
@@ -31134,7 +32998,7 @@
         <v>2476</v>
       </c>
     </row>
-    <row r="821" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A821" t="s">
         <v>626</v>
       </c>
@@ -31145,7 +33009,7 @@
         <v>2477</v>
       </c>
     </row>
-    <row r="822" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A822" t="s">
         <v>626</v>
       </c>
@@ -31156,7 +33020,7 @@
         <v>2478</v>
       </c>
     </row>
-    <row r="823" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A823" t="s">
         <v>626</v>
       </c>
@@ -31167,7 +33031,7 @@
         <v>2479</v>
       </c>
     </row>
-    <row r="824" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A824" t="s">
         <v>626</v>
       </c>
@@ -31178,7 +33042,7 @@
         <v>2480</v>
       </c>
     </row>
-    <row r="825" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A825" t="s">
         <v>626</v>
       </c>
@@ -31189,7 +33053,7 @@
         <v>2481</v>
       </c>
     </row>
-    <row r="826" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A826" t="s">
         <v>626</v>
       </c>
@@ -31200,7 +33064,7 @@
         <v>2482</v>
       </c>
     </row>
-    <row r="827" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A827" t="s">
         <v>626</v>
       </c>
@@ -31211,7 +33075,7 @@
         <v>2483</v>
       </c>
     </row>
-    <row r="828" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A828" t="s">
         <v>626</v>
       </c>
@@ -31222,7 +33086,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="829" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A829" t="s">
         <v>626</v>
       </c>
@@ -31233,7 +33097,7 @@
         <v>2485</v>
       </c>
     </row>
-    <row r="830" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A830" t="s">
         <v>626</v>
       </c>
@@ -31244,7 +33108,7 @@
         <v>2486</v>
       </c>
     </row>
-    <row r="831" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A831" t="s">
         <v>626</v>
       </c>
@@ -31255,7 +33119,7 @@
         <v>2487</v>
       </c>
     </row>
-    <row r="832" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A832" t="s">
         <v>626</v>
       </c>
@@ -31266,7 +33130,7 @@
         <v>2488</v>
       </c>
     </row>
-    <row r="833" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A833" t="s">
         <v>626</v>
       </c>
@@ -31277,7 +33141,7 @@
         <v>2489</v>
       </c>
     </row>
-    <row r="834" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A834" t="s">
         <v>626</v>
       </c>
@@ -31288,7 +33152,7 @@
         <v>2490</v>
       </c>
     </row>
-    <row r="835" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A835" t="s">
         <v>626</v>
       </c>
@@ -31299,7 +33163,7 @@
         <v>2491</v>
       </c>
     </row>
-    <row r="836" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A836" t="s">
         <v>626</v>
       </c>
@@ -31310,7 +33174,7 @@
         <v>2492</v>
       </c>
     </row>
-    <row r="837" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A837" t="s">
         <v>626</v>
       </c>
@@ -31321,7 +33185,7 @@
         <v>2493</v>
       </c>
     </row>
-    <row r="838" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A838" t="s">
         <v>626</v>
       </c>
@@ -31332,7 +33196,7 @@
         <v>2494</v>
       </c>
     </row>
-    <row r="839" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A839" t="s">
         <v>626</v>
       </c>
@@ -31343,7 +33207,7 @@
         <v>2495</v>
       </c>
     </row>
-    <row r="840" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A840" t="s">
         <v>626</v>
       </c>
@@ -31354,7 +33218,7 @@
         <v>2496</v>
       </c>
     </row>
-    <row r="841" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A841" t="s">
         <v>626</v>
       </c>
@@ -31365,7 +33229,7 @@
         <v>2497</v>
       </c>
     </row>
-    <row r="842" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A842" t="s">
         <v>626</v>
       </c>
@@ -31376,7 +33240,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="843" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A843" t="s">
         <v>626</v>
       </c>
@@ -31387,7 +33251,7 @@
         <v>2499</v>
       </c>
     </row>
-    <row r="844" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A844" t="s">
         <v>626</v>
       </c>
@@ -31398,7 +33262,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="845" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A845" t="s">
         <v>626</v>
       </c>
@@ -31409,7 +33273,7 @@
         <v>2501</v>
       </c>
     </row>
-    <row r="846" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A846" t="s">
         <v>626</v>
       </c>
@@ -31420,7 +33284,7 @@
         <v>2502</v>
       </c>
     </row>
-    <row r="847" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A847" t="s">
         <v>626</v>
       </c>
@@ -31431,7 +33295,7 @@
         <v>2503</v>
       </c>
     </row>
-    <row r="848" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A848" t="s">
         <v>626</v>
       </c>
@@ -31442,7 +33306,7 @@
         <v>2504</v>
       </c>
     </row>
-    <row r="849" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A849" t="s">
         <v>626</v>
       </c>
@@ -31453,7 +33317,7 @@
         <v>2505</v>
       </c>
     </row>
-    <row r="850" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A850" t="s">
         <v>626</v>
       </c>
@@ -31464,7 +33328,7 @@
         <v>2506</v>
       </c>
     </row>
-    <row r="851" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A851" t="s">
         <v>626</v>
       </c>
@@ -31475,7 +33339,7 @@
         <v>2507</v>
       </c>
     </row>
-    <row r="852" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A852" t="s">
         <v>626</v>
       </c>
@@ -31486,7 +33350,7 @@
         <v>2508</v>
       </c>
     </row>
-    <row r="853" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A853" t="s">
         <v>626</v>
       </c>
@@ -31497,7 +33361,7 @@
         <v>2509</v>
       </c>
     </row>
-    <row r="854" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A854" t="s">
         <v>626</v>
       </c>
@@ -31508,7 +33372,7 @@
         <v>2510</v>
       </c>
     </row>
-    <row r="855" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A855" t="s">
         <v>626</v>
       </c>
@@ -31519,7 +33383,7 @@
         <v>2511</v>
       </c>
     </row>
-    <row r="856" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A856" t="s">
         <v>626</v>
       </c>
@@ -31530,7 +33394,7 @@
         <v>2512</v>
       </c>
     </row>
-    <row r="857" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A857" t="s">
         <v>626</v>
       </c>
@@ -31541,7 +33405,7 @@
         <v>2513</v>
       </c>
     </row>
-    <row r="858" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A858" t="s">
         <v>626</v>
       </c>
@@ -31552,7 +33416,7 @@
         <v>2514</v>
       </c>
     </row>
-    <row r="859" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A859" t="s">
         <v>626</v>
       </c>
@@ -31563,7 +33427,7 @@
         <v>2515</v>
       </c>
     </row>
-    <row r="860" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A860" t="s">
         <v>626</v>
       </c>
@@ -31574,7 +33438,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="861" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A861" t="s">
         <v>626</v>
       </c>
@@ -31585,7 +33449,7 @@
         <v>2517</v>
       </c>
     </row>
-    <row r="862" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A862" t="s">
         <v>626</v>
       </c>
@@ -31596,7 +33460,7 @@
         <v>2518</v>
       </c>
     </row>
-    <row r="863" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A863" t="s">
         <v>626</v>
       </c>
@@ -31607,7 +33471,7 @@
         <v>2519</v>
       </c>
     </row>
-    <row r="864" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A864" t="s">
         <v>626</v>
       </c>
@@ -31618,7 +33482,7 @@
         <v>2520</v>
       </c>
     </row>
-    <row r="865" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A865" t="s">
         <v>626</v>
       </c>
@@ -31629,7 +33493,7 @@
         <v>2521</v>
       </c>
     </row>
-    <row r="866" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A866" t="s">
         <v>626</v>
       </c>
@@ -31640,7 +33504,7 @@
         <v>2522</v>
       </c>
     </row>
-    <row r="867" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A867" t="s">
         <v>626</v>
       </c>
@@ -31651,7 +33515,7 @@
         <v>2523</v>
       </c>
     </row>
-    <row r="868" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A868" t="s">
         <v>626</v>
       </c>
@@ -31662,7 +33526,7 @@
         <v>2524</v>
       </c>
     </row>
-    <row r="869" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A869" t="s">
         <v>626</v>
       </c>
@@ -31673,7 +33537,7 @@
         <v>2525</v>
       </c>
     </row>
-    <row r="870" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A870" t="s">
         <v>626</v>
       </c>
@@ -31684,7 +33548,7 @@
         <v>2526</v>
       </c>
     </row>
-    <row r="871" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A871" t="s">
         <v>626</v>
       </c>
@@ -31695,7 +33559,7 @@
         <v>2527</v>
       </c>
     </row>
-    <row r="872" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A872" t="s">
         <v>626</v>
       </c>
@@ -31706,7 +33570,7 @@
         <v>2528</v>
       </c>
     </row>
-    <row r="873" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A873" t="s">
         <v>626</v>
       </c>
@@ -31717,7 +33581,7 @@
         <v>2529</v>
       </c>
     </row>
-    <row r="874" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A874" t="s">
         <v>626</v>
       </c>
@@ -31728,7 +33592,7 @@
         <v>2530</v>
       </c>
     </row>
-    <row r="875" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A875" t="s">
         <v>626</v>
       </c>
@@ -31739,7 +33603,7 @@
         <v>2531</v>
       </c>
     </row>
-    <row r="876" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A876" t="s">
         <v>626</v>
       </c>
@@ -31750,7 +33614,7 @@
         <v>2532</v>
       </c>
     </row>
-    <row r="877" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A877" t="s">
         <v>626</v>
       </c>
@@ -31761,7 +33625,7 @@
         <v>2533</v>
       </c>
     </row>
-    <row r="878" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A878" t="s">
         <v>626</v>
       </c>
@@ -31772,7 +33636,7 @@
         <v>2534</v>
       </c>
     </row>
-    <row r="879" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A879" t="s">
         <v>626</v>
       </c>
@@ -31783,7 +33647,7 @@
         <v>2535</v>
       </c>
     </row>
-    <row r="880" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A880" t="s">
         <v>626</v>
       </c>
@@ -31794,7 +33658,7 @@
         <v>2536</v>
       </c>
     </row>
-    <row r="881" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A881" t="s">
         <v>626</v>
       </c>
@@ -31805,7 +33669,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="882" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A882" t="s">
         <v>626</v>
       </c>
@@ -31816,7 +33680,7 @@
         <v>2538</v>
       </c>
     </row>
-    <row r="883" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A883" t="s">
         <v>626</v>
       </c>
@@ -31827,7 +33691,7 @@
         <v>2539</v>
       </c>
     </row>
-    <row r="884" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A884" t="s">
         <v>626</v>
       </c>
@@ -31838,7 +33702,7 @@
         <v>2540</v>
       </c>
     </row>
-    <row r="885" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A885" t="s">
         <v>626</v>
       </c>
@@ -31849,7 +33713,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="886" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A886" t="s">
         <v>626</v>
       </c>
@@ -31860,7 +33724,7 @@
         <v>2542</v>
       </c>
     </row>
-    <row r="887" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A887" t="s">
         <v>626</v>
       </c>
@@ -31871,7 +33735,7 @@
         <v>2543</v>
       </c>
     </row>
-    <row r="888" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A888" t="s">
         <v>626</v>
       </c>
@@ -31882,7 +33746,7 @@
         <v>2544</v>
       </c>
     </row>
-    <row r="889" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A889" t="s">
         <v>626</v>
       </c>
@@ -31893,7 +33757,7 @@
         <v>2545</v>
       </c>
     </row>
-    <row r="890" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A890" t="s">
         <v>626</v>
       </c>
@@ -33193,100 +35057,180 @@
   </sheetData>
   <autoFilter ref="A1:O930" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="A1:O1 A2:J13 L2:O13 A14:O15 L16:O38 L43:O46 K47:O53 A54:O63 A64:J65 L64:O65 K72:O77 A73:I73 A74:H74 A75:I75 A76:H76 A77:I77 A78:O106 A107:I132 K107:O132 A133:O171 A172:I172 K172:O172 A188:J190 L188:O190 A232:J232 L232:O232 A233:O233 A234:J235 L234:O235 A236:O246 A247:I247 K247:O247 A248:O248 A249:I249 K249:O249 A250:O250 A251:I251 K251:O251 A252:O252 A253:I253 K253:O253 A254:O254 A255:I255 K255:O255 A256:J256 L256:O256 A257:O259 A260:J261 L260:O261 L296:O298 A304:H304 L304:O304 A305:O305 A306:H306 L306:O306 A307:O307 A308:H308 L308:O308 A309:O314 A315:H315 L315:O315 A316:O323 A324:H339 L324:O341 A340:I341 A343:I343 L343:O343 A345:I345 L345:O345 A346:O347 A348:I348 K348:O348 A349:O351 A352:I352 K352:O352 A353:O353 A354:I354 K354:O354 A355:O355 A356:I356 K356:O356 A357:O357 A358:J362 L358:O362 A363:O370 A371:J391 L371:O391 A392:O392 A393:J393 L393:O393 A394:O396 A397:I397 L397:O397 A398:O398 A399:I399 L399:O399 A400:O400 A401:I401 L401:O401 A402:O402 A403:I403 L403:O403 A404:O404 A405:I405 L405:O406 A406:J406 A407:O409 A410:J413 L410:O413 A414:O414 A415:J419 L415:O419 A420:O420 A421:J422 L421:O422 A423:O423 A424:J425 L424:O425 A426:O427 A428:J428 L428:O428 A429:O429 A430:J432 L430:O432 A433:O434 A435:J442 L435:O442 A443:O443 A444:J444 L444:O444 A445:O448 A449:J450 L449:O450 A451:O451 A452:J457 L452:O457 A458:O461 A462:J474 L462:O474 A475:O483 A484:J512 L484:O512 A513:O519 A520:J522 L520:O522 A523:O563 A564:J575 L564:O575 A576:O576 A577:J583 L577:O583 A584:O598 A599:J612 L599:O612 A613:O620 A621:J631 L621:O631 A632:O640 A641:J641 L641:O641 A642:O642 A643:J643 L643:O643 A644:O893 A894:J896 L894:O896 A897:O897 A898:J903 L898:O903 A904:O908 A909:I910 K909:O910 A911:O918 J919 A919:I922 K919:O922 A923:J928 L923:O928 A929:O1048576 A262:O263 A288:H289 J288:O289 A264:H264 J264:O264 A285:H285 J285:O285 A297:J297 A191:O197 A201:O201 A200:H200 J200:O200 A203:O204 A202:H202 J202:O202 A212:O212 A211:H211 J211:O211 A225:O231 A223:H224 J223:O224 A215:O218 A208:O210 A207:H207 J207:O207 A213:H214 J213:O214 A220:O222 A219:H219 J219:O219 A199:O199 A198:H198 J198:O198 A206:O206 A205:H205 J205:O205 A290:O295 A265:O274 A275:H275 J275:O275 A276:O284 A286:O287 A296:H296 J296 A298:H298 J298 A342:O342 A344:O344 A16:J24 A25:I26 A27:J38 A39:O42 A43:J46 A47:I49 A51:I51 A50:H50 A53:I53 A52:H52 A66:O71 A72:J72 J74 J76 A173:O187">
-    <cfRule type="expression" dxfId="1" priority="22">
+  <conditionalFormatting sqref="A1:O1 A2:J13 L2:O13 A14:O15 A16:J24 L16:O38 A25:I26 A27:J38 A43:J46 L43:O46 K47:O53 A51:I51 A53:I53 A64:J65 L64:O65 K72:O77 A73:I73 J74 A75:I75 J76 A77:I77 A78:O106 A107:I132 K107:O132 A133:O171 A172:I172 K172:O172 A188:J190 L188:O190 A191:O197 A198:H198 J198:O198 A199:O199 A200:H200 J200:O200 A201:O201 A202:H202 J202:O202 A203:O204 A205:H205 J205:O205 A206:O206 A207:H207 J207:O207 A208:O210 A211:H211 J211:O211 A212:O212 A213:H214 J213:O214 A215:O218 A219:H219 J219:O219 A220:O222 A223:H224 J223:O224 A225:O231 A232:J232 L232:O232 A233:O233 A234:J235 L234:O235 A247:I247 K247:O247 A249:I249 K249:O249 K251:O251 K253:O253 K255:O255 A256:J256 L256:O256 A257:O259 A260:J261 L260:O261 A275:H275 J275:O275 A296:H296 J296 L296:O298 A297:C297 A298:H298 J298 A304:H304 L304:O304 A305:O305 A306:H306 L306:O306 A307:O307 A308:H308 L308:O308 A315:H315 L315:O315 A324:H339 L324:O341 A340:I341 A342:O342 A343:I343 L343:O343 A344:O344 A345:I345 L345:O345 A346:O347 A348:I348 K348:O348 A352:I352 K352:O352 A354:I354 K354:O354 A356:I356 K356:O356 A358:J362 L358:O362 A371:J391 L371:O391 A392:O392 A393:J393 L393:O393 A397:I397 L397:O397 L399:O399 L401:O401 L403:O403 L405:O406 A406:J406 A407:O409 A410:J413 L410:O413 L415:O419 A420:O420 A421:J422 L421:O422 A423:O423 L424:O425 L428:O428 L430:O432 L435:O442 A443:H443 A444:J444 L444:O444 A449:J450 L449:O450 A451:O451 A452:J457 L452:O457 A462:J474 L462:O474 A484:J512 L484:O512 A520:J522 L520:O522 L564:O575 A576:O576 A578:J578 L577:O583 A599:J612 L599:O612 A613:O620 A621:J631 L621:O631 A641:J641 L641:O641 A894:J896 L894:O896 A897:O897 A898:J903 L898:O903 A904:O908 A909:I910 K909:O910 A911:O918 J919 A919:I922 K919:O922 A923:J928 L923:O928 A929:O1048576 A39:O42 A54:O63 A66:O71 A72:J72 A74:H74 A76:H76 A173:O187 E297:J297 A309:O314 A316:O323 A349:O351 A353:O353 A355:O355 A357:O357 A475:O475 A514:O514 A523:O527 A537:C537 E537:O537 A529:O536 A528:C528 E528:O528 A47:I49 A50:H50 A52:H52 A584:O598 A632:O640 A394:O396 A398:O398 A400:O400 A402:O402 A404:O404 A399:I399 A401:I401 A403:I403 A405:I405 A416:J419 A428:J428 A435:J436 A415:H415 J415 A438:J442 A437:H437 J437 A424:J425 A430:J432 A414:O414 A429:O429 A433:O434 J443:O443 A445:H445 J445:O445 A446:O448 A426:O427 A458:O461 A478:O483 A476:H477 J476:O477 A513:H513 J513:O513 A518:O519 A517:H517 J517:O517 A516:O516 A515:H515 J515:O515 A564:J564 A546:H546 J546:O546 A570:J571 A574:J575 A568:H569 J568:J569 A572:H573 J572:J573 A538:O545 A547:O563 A567:J567 A565:H566 J565:J566 A577:H577 J577 A580:J583 A579:H579 J579 A236:O246 A248:O248 A250:O250 A252:O252 A254:O254 A251:I251 A253:I253 A255:I255 A363:O370 A642:O893 K495">
+    <cfRule type="expression" dxfId="3" priority="50">
       <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O1))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="23">
+    <cfRule type="expression" dxfId="2" priority="51">
       <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O1))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A299:O299 A303:O303 A300:H302 J300:O302">
-    <cfRule type="expression" dxfId="25" priority="17">
+  <conditionalFormatting sqref="A262:O274">
+    <cfRule type="expression" dxfId="43" priority="35">
+      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O262))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="42" priority="36">
+      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O262))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A276:O276 A281:O282 A277:C280 E277:O280 A284:O284 A283:C283 E283:O283 A286:O287 A285:C285 E285:O285 A290:O290 A288:C289 E288:O289 A294:O294 A291:C293 E291:O293 A295:C295 E295:O295">
+    <cfRule type="expression" dxfId="41" priority="33">
+      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O276))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="40" priority="34">
+      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O276))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A299:O303">
+    <cfRule type="expression" dxfId="39" priority="29">
       <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O299))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="18">
+    <cfRule type="expression" dxfId="38" priority="30">
       <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O299))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J26 J920:J922">
-    <cfRule type="expression" dxfId="23" priority="26">
+    <cfRule type="expression" dxfId="37" priority="54">
       <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O25))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="27">
+    <cfRule type="expression" dxfId="36" priority="55">
       <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O25))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J909:J910">
-    <cfRule type="expression" dxfId="21" priority="30">
+    <cfRule type="expression" dxfId="35" priority="58">
       <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O910))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="31">
+    <cfRule type="expression" dxfId="34" priority="59">
       <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O910))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K341">
-    <cfRule type="expression" dxfId="19" priority="15">
+    <cfRule type="expression" dxfId="33" priority="43">
       <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O341))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="16">
+    <cfRule type="expression" dxfId="32" priority="44">
       <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O341))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K923:K928">
-    <cfRule type="expression" dxfId="17" priority="13">
+    <cfRule type="expression" dxfId="31" priority="41">
       <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O922))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="14">
+    <cfRule type="expression" dxfId="30" priority="42">
       <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O922))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I302">
-    <cfRule type="expression" dxfId="15" priority="11">
-      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O302))</formula>
+  <conditionalFormatting sqref="D277">
+    <cfRule type="expression" dxfId="29" priority="27">
+      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O277))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="12">
-      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O302))</formula>
+    <cfRule type="expression" dxfId="28" priority="28">
+      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O277))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I288:I289">
-    <cfRule type="expression" dxfId="13" priority="9">
+  <conditionalFormatting sqref="D278">
+    <cfRule type="expression" dxfId="27" priority="25">
+      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O278))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="26">
+      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O278))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D279">
+    <cfRule type="expression" dxfId="25" priority="23">
+      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O279))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="24">
+      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O279))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D280">
+    <cfRule type="expression" dxfId="23" priority="21">
+      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O280))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="22">
+      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O280))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D283">
+    <cfRule type="expression" dxfId="21" priority="19">
+      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O283))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="20">
+      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O283))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D285">
+    <cfRule type="expression" dxfId="19" priority="17">
+      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O285))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="18">
+      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O285))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D288">
+    <cfRule type="expression" dxfId="17" priority="15">
       <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O288))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="10">
+    <cfRule type="expression" dxfId="16" priority="16">
       <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O288))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I264">
-    <cfRule type="expression" dxfId="11" priority="7">
-      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O264))</formula>
+  <conditionalFormatting sqref="D289">
+    <cfRule type="expression" dxfId="15" priority="13">
+      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O289))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="8">
-      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O264))</formula>
+    <cfRule type="expression" dxfId="14" priority="14">
+      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O289))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I285">
-    <cfRule type="expression" dxfId="9" priority="5">
-      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O285))</formula>
+  <conditionalFormatting sqref="D292">
+    <cfRule type="expression" dxfId="13" priority="11">
+      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O292))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="6">
-      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O285))</formula>
+    <cfRule type="expression" dxfId="12" priority="12">
+      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O292))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I301">
-    <cfRule type="expression" dxfId="7" priority="3">
-      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O301))</formula>
+  <conditionalFormatting sqref="D291">
+    <cfRule type="expression" dxfId="11" priority="9">
+      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O291))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="4">
-      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O301))</formula>
+    <cfRule type="expression" dxfId="10" priority="10">
+      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O291))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I300">
-    <cfRule type="expression" dxfId="5" priority="1">
-      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O300))</formula>
+  <conditionalFormatting sqref="D293">
+    <cfRule type="expression" dxfId="9" priority="7">
+      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O293))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
-      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O300))</formula>
+    <cfRule type="expression" dxfId="8" priority="8">
+      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O293))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D295">
+    <cfRule type="expression" dxfId="7" priority="5">
+      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O295))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="6">
+      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O295))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D297">
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O297))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="4">
+      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O297))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K297">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O297))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O297))</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>

--- a/data/missing_meta/missing_meta.xlsx
+++ b/data/missing_meta/missing_meta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marco_schuppisser/Desktop/Repository sabseb (new)/metasabseb/data/missing_meta/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F05E10-1A20-6549-AE13-36597237F4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{107E5FF8-2E6D-6442-BDD4-FF94BC7BA2B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="68640" yWindow="-3860" windowWidth="38400" windowHeight="23500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8212" uniqueCount="2662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8242" uniqueCount="2681">
   <si>
     <t>var_defs_key</t>
   </si>
@@ -8524,6 +8524,63 @@
   </si>
   <si>
     <t>Einzelitem: Unterrichtssprache</t>
+  </si>
+  <si>
+    <t>Afrika</t>
+  </si>
+  <si>
+    <t>Asien</t>
+  </si>
+  <si>
+    <t>Andere Sprachregion der Schweiz</t>
+  </si>
+  <si>
+    <t>Europa</t>
+  </si>
+  <si>
+    <t>Lateinamerika (Mittel- und Südamerika)</t>
+  </si>
+  <si>
+    <t>Nordamerika</t>
+  </si>
+  <si>
+    <t>Ozeanien</t>
+  </si>
+  <si>
+    <t>Andere</t>
+  </si>
+  <si>
+    <t>Austauschorganisation (AFS, YFU etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lehrbetrieb </t>
+  </si>
+  <si>
+    <t>Schule</t>
+  </si>
+  <si>
+    <t>eine Gruppenmobilität</t>
+  </si>
+  <si>
+    <t>Mehr als zwei Einzelmobilitäten</t>
+  </si>
+  <si>
+    <t>Mehr als 2 Gruppenmobilität</t>
+  </si>
+  <si>
+    <t>Einzelmobilität als Praktikum</t>
+  </si>
+  <si>
+    <t>Einzelmobilität durch Besuch der lokalen Schule</t>
+  </si>
+  <si>
+    <t>Einzelmobilität in einer Sprachschule</t>
+  </si>
+  <si>
+    <t>zwei Einzelmobilitäten</t>
+  </si>
+  <si>
+    <t>zwei Gruppenmobilitäten</t>
   </si>
 </sst>
 </file>
@@ -8677,7 +8734,17 @@
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="2" xr:uid="{BC66F5EB-00B7-4041-B960-07C65FD467B2}"/>
   </cellStyles>
-  <dxfs count="44">
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -8685,6 +8752,26 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -8770,16 +8857,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -8800,16 +8877,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -8825,276 +8892,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -11468,6 +11265,9 @@
       <c r="E54" t="s">
         <v>2199</v>
       </c>
+      <c r="F54" t="s">
+        <v>2673</v>
+      </c>
       <c r="G54" t="s">
         <v>1402</v>
       </c>
@@ -11497,6 +11297,9 @@
       <c r="E55" t="s">
         <v>2199</v>
       </c>
+      <c r="F55" t="s">
+        <v>2674</v>
+      </c>
       <c r="G55" t="s">
         <v>1402</v>
       </c>
@@ -11526,6 +11329,9 @@
       <c r="E56" t="s">
         <v>2199</v>
       </c>
+      <c r="F56" t="s">
+        <v>2675</v>
+      </c>
       <c r="G56" t="s">
         <v>1402</v>
       </c>
@@ -11555,6 +11361,9 @@
       <c r="E57" t="s">
         <v>2199</v>
       </c>
+      <c r="F57" t="s">
+        <v>2676</v>
+      </c>
       <c r="G57" t="s">
         <v>1402</v>
       </c>
@@ -11584,6 +11393,9 @@
       <c r="E58" t="s">
         <v>2199</v>
       </c>
+      <c r="F58" t="s">
+        <v>2677</v>
+      </c>
       <c r="G58" t="s">
         <v>1402</v>
       </c>
@@ -11613,6 +11425,9 @@
       <c r="E59" t="s">
         <v>2199</v>
       </c>
+      <c r="F59" t="s">
+        <v>2678</v>
+      </c>
       <c r="G59" t="s">
         <v>1402</v>
       </c>
@@ -11642,6 +11457,9 @@
       <c r="E60" t="s">
         <v>2199</v>
       </c>
+      <c r="F60" t="s">
+        <v>2679</v>
+      </c>
       <c r="G60" t="s">
         <v>1402</v>
       </c>
@@ -11670,6 +11488,9 @@
       </c>
       <c r="E61" t="s">
         <v>2199</v>
+      </c>
+      <c r="F61" t="s">
+        <v>2680</v>
       </c>
       <c r="G61" t="s">
         <v>1402</v>
@@ -19967,6 +19788,12 @@
       <c r="D320" t="s">
         <v>2646</v>
       </c>
+      <c r="E320" t="s">
+        <v>543</v>
+      </c>
+      <c r="F320" t="s">
+        <v>2669</v>
+      </c>
       <c r="G320" t="s">
         <v>1402</v>
       </c>
@@ -19993,6 +19820,12 @@
       <c r="D321" t="s">
         <v>2646</v>
       </c>
+      <c r="E321" t="s">
+        <v>543</v>
+      </c>
+      <c r="F321" t="s">
+        <v>2670</v>
+      </c>
       <c r="G321" t="s">
         <v>1402</v>
       </c>
@@ -20019,6 +19852,12 @@
       <c r="D322" t="s">
         <v>2646</v>
       </c>
+      <c r="E322" t="s">
+        <v>543</v>
+      </c>
+      <c r="F322" t="s">
+        <v>2671</v>
+      </c>
       <c r="G322" t="s">
         <v>1402</v>
       </c>
@@ -20044,6 +19883,12 @@
       </c>
       <c r="D323" t="s">
         <v>2646</v>
+      </c>
+      <c r="E323" t="s">
+        <v>543</v>
+      </c>
+      <c r="F323" t="s">
+        <v>2672</v>
       </c>
       <c r="G323" t="s">
         <v>1402</v>
@@ -29584,6 +29429,12 @@
       <c r="D585" t="s">
         <v>2653</v>
       </c>
+      <c r="E585" t="s">
+        <v>2276</v>
+      </c>
+      <c r="F585" t="s">
+        <v>2662</v>
+      </c>
       <c r="G585" t="s">
         <v>1402</v>
       </c>
@@ -29610,6 +29461,12 @@
       <c r="D586" t="s">
         <v>2653</v>
       </c>
+      <c r="E586" t="s">
+        <v>2276</v>
+      </c>
+      <c r="F586" t="s">
+        <v>2663</v>
+      </c>
       <c r="G586" t="s">
         <v>1402</v>
       </c>
@@ -29636,6 +29493,12 @@
       <c r="D587" t="s">
         <v>2653</v>
       </c>
+      <c r="E587" t="s">
+        <v>2276</v>
+      </c>
+      <c r="F587" t="s">
+        <v>2664</v>
+      </c>
       <c r="G587" t="s">
         <v>1402</v>
       </c>
@@ -29662,6 +29525,12 @@
       <c r="D588" t="s">
         <v>2653</v>
       </c>
+      <c r="E588" t="s">
+        <v>2276</v>
+      </c>
+      <c r="F588" t="s">
+        <v>2665</v>
+      </c>
       <c r="G588" t="s">
         <v>1402</v>
       </c>
@@ -29688,6 +29557,12 @@
       <c r="D589" t="s">
         <v>2653</v>
       </c>
+      <c r="E589" t="s">
+        <v>2276</v>
+      </c>
+      <c r="F589" t="s">
+        <v>2666</v>
+      </c>
       <c r="G589" t="s">
         <v>1402</v>
       </c>
@@ -29714,6 +29589,12 @@
       <c r="D590" t="s">
         <v>2653</v>
       </c>
+      <c r="E590" t="s">
+        <v>2276</v>
+      </c>
+      <c r="F590" t="s">
+        <v>2667</v>
+      </c>
       <c r="G590" t="s">
         <v>1402</v>
       </c>
@@ -29740,6 +29621,12 @@
       <c r="D591" t="s">
         <v>2653</v>
       </c>
+      <c r="E591" t="s">
+        <v>2276</v>
+      </c>
+      <c r="F591" t="s">
+        <v>2668</v>
+      </c>
       <c r="G591" t="s">
         <v>1402</v>
       </c>
@@ -35057,180 +34944,76 @@
   </sheetData>
   <autoFilter ref="A1:O930" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="A1:O1 A2:J13 L2:O13 A14:O15 A16:J24 L16:O38 A25:I26 A27:J38 A43:J46 L43:O46 K47:O53 A51:I51 A53:I53 A64:J65 L64:O65 K72:O77 A73:I73 J74 A75:I75 J76 A77:I77 A78:O106 A107:I132 K107:O132 A133:O171 A172:I172 K172:O172 A188:J190 L188:O190 A191:O197 A198:H198 J198:O198 A199:O199 A200:H200 J200:O200 A201:O201 A202:H202 J202:O202 A203:O204 A205:H205 J205:O205 A206:O206 A207:H207 J207:O207 A208:O210 A211:H211 J211:O211 A212:O212 A213:H214 J213:O214 A215:O218 A219:H219 J219:O219 A220:O222 A223:H224 J223:O224 A225:O231 A232:J232 L232:O232 A233:O233 A234:J235 L234:O235 A247:I247 K247:O247 A249:I249 K249:O249 K251:O251 K253:O253 K255:O255 A256:J256 L256:O256 A257:O259 A260:J261 L260:O261 A275:H275 J275:O275 A296:H296 J296 L296:O298 A297:C297 A298:H298 J298 A304:H304 L304:O304 A305:O305 A306:H306 L306:O306 A307:O307 A308:H308 L308:O308 A315:H315 L315:O315 A324:H339 L324:O341 A340:I341 A342:O342 A343:I343 L343:O343 A344:O344 A345:I345 L345:O345 A346:O347 A348:I348 K348:O348 A352:I352 K352:O352 A354:I354 K354:O354 A356:I356 K356:O356 A358:J362 L358:O362 A371:J391 L371:O391 A392:O392 A393:J393 L393:O393 A397:I397 L397:O397 L399:O399 L401:O401 L403:O403 L405:O406 A406:J406 A407:O409 A410:J413 L410:O413 L415:O419 A420:O420 A421:J422 L421:O422 A423:O423 L424:O425 L428:O428 L430:O432 L435:O442 A443:H443 A444:J444 L444:O444 A449:J450 L449:O450 A451:O451 A452:J457 L452:O457 A462:J474 L462:O474 A484:J512 L484:O512 A520:J522 L520:O522 L564:O575 A576:O576 A578:J578 L577:O583 A599:J612 L599:O612 A613:O620 A621:J631 L621:O631 A641:J641 L641:O641 A894:J896 L894:O896 A897:O897 A898:J903 L898:O903 A904:O908 A909:I910 K909:O910 A911:O918 J919 A919:I922 K919:O922 A923:J928 L923:O928 A929:O1048576 A39:O42 A54:O63 A66:O71 A72:J72 A74:H74 A76:H76 A173:O187 E297:J297 A309:O314 A316:O323 A349:O351 A353:O353 A355:O355 A357:O357 A475:O475 A514:O514 A523:O527 A537:C537 E537:O537 A529:O536 A528:C528 E528:O528 A47:I49 A50:H50 A52:H52 A584:O598 A632:O640 A394:O396 A398:O398 A400:O400 A402:O402 A404:O404 A399:I399 A401:I401 A403:I403 A405:I405 A416:J419 A428:J428 A435:J436 A415:H415 J415 A438:J442 A437:H437 J437 A424:J425 A430:J432 A414:O414 A429:O429 A433:O434 J443:O443 A445:H445 J445:O445 A446:O448 A426:O427 A458:O461 A478:O483 A476:H477 J476:O477 A513:H513 J513:O513 A518:O519 A517:H517 J517:O517 A516:O516 A515:H515 J515:O515 A564:J564 A546:H546 J546:O546 A570:J571 A574:J575 A568:H569 J568:J569 A572:H573 J572:J573 A538:O545 A547:O563 A567:J567 A565:H566 J565:J566 A577:H577 J577 A580:J583 A579:H579 J579 A236:O246 A248:O248 A250:O250 A252:O252 A254:O254 A251:I251 A253:I253 A255:I255 A363:O370 A642:O893 K495">
-    <cfRule type="expression" dxfId="3" priority="50">
+  <conditionalFormatting sqref="A297:K297">
+    <cfRule type="expression" dxfId="17" priority="1">
+      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O297))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="2">
+      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O297))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:O1 A2:J13 L2:O13 A14:O15 A16:J24 L16:O38 A25:I26 A27:J38 A39:O42 A43:J46 L43:O46 A47:I49 K47:O53 A50:H50 A51:I51 A52:H52 A53:I53 A54:O63 A64:J65 L64:O65 A66:O71 A72:J72 K72:O77 A73:I73 A74:H74 J74 A75:I75 A76:H76 J76 A77:I77 A78:O106 A107:I132 K107:O132 A133:O171 A172:I172 K172:O172 A173:O187 A188:J190 L188:O190 A191:O197 A198:H198 J198:O198 A199:O199 A200:H200 J200:O200 A201:O201 A202:H202 J202:O202 A203:O204 A205:H205 J205:O205 A206:O206 A207:H207 J207:O207 A208:O210 A211:H211 J211:O211 A212:O212 A213:H214 J213:O214 A215:O218 A219:H219 J219:O219 A220:O222 A223:H224 J223:O224 A225:O231 A232:J232 L232:O232 A233:O233 A234:J235 L234:O235 A236:O246 A247:I247 K247:O247 A248:O248 A249:I249 K249:O249 A250:O250 A251:I251 K251:O251 A252:O252 A253:I253 K253:O253 A254:O254 A255:I255 K255:O255 A256:J256 L256:O256 A257:O259 A260:J261 L260:O261 A275:H275 J275:O275 A296:H296 J296 L296:O298 A298:H298 J298 A304:H304 L304:O304 A305:O305 A306:H306 L306:O306 A307:O307 A308:H308 L308:O308 A309:O314 A315:H315 L315:O315 A324:H339 L324:O341 A340:I341 A342:O342 A343:I343 L343:O343 A344:O344 A345:I345 L345:O345 A346:O347 A348:I348 K348:O348 A349:O351 A352:I352 K352:O352 A353:O353 A354:I354 K354:O354 A355:O355 A356:I356 K356:O356 A357:O357 A358:J362 L358:O362 A363:O370 A371:J391 L371:O391 A392:O392 A393:J393 L393:O393 A394:O396 A397:I397 L397:O397 A398:O398 A399:I399 L399:O399 A400:O400 A401:I401 L401:O401 A402:O402 A403:I403 L403:O403 A404:O404 A405:I405 L405:O406 A406:J406 A407:O409 A410:J413 L410:O413 A414:O414 A415:H415 J415 L415:O419 A416:J419 A420:O420 A421:J422 L421:O422 A423:O423 A424:J425 L424:O425 A426:O427 A428:J428 L428:O428 A429:O429 A430:J432 L430:O432 A433:O434 A435:J436 L435:O442 A437:H437 J437 A438:J442 A443:H443 J443:O443 A444:J444 L444:O444 A445:H445 J445:O445 A446:O448 A449:J450 L449:O450 A451:O451 A452:J457 L452:O457 A458:O461 A462:J474 L462:O474 A475:O475 A476:H477 J476:O477 A478:O483 A484:J512 L484:O512 K495 A513:H513 J513:O513 A514:O514 A515:H515 J515:O515 A516:O516 A517:H517 J517:O517 A518:O519 A520:J522 L520:O522 A523:O527 A528:C528 E528:O528 A529:O536 A537:C537 E537:O537 A538:O545 A546:H546 J546:O546 A547:O563 A564:J564 L564:O575 A565:H566 J565:J566 A567:J567 A568:H569 J568:J569 A570:J571 A572:H573 J572:J573 A574:J575 A576:O576 A577:H577 J577 L577:O583 A578:J578 A579:H579 J579 A580:J583 A599:J612 L599:O612 A613:O620 A621:J631 L621:O631 A632:O640 A641:J641 L641:O641 A642:O893 A894:J896 L894:O896 A897:O897 A898:J903 L898:O903 A904:O908 A909:I910 K909:O910 A911:O918 J919 A919:I922 K919:O922 A923:J928 L923:O928 A929:O1048576 A316:O323 A584:O598">
+    <cfRule type="expression" dxfId="1" priority="51">
+      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O1))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="50">
       <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O1))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="51">
-      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O1))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A262:O274">
-    <cfRule type="expression" dxfId="43" priority="35">
+    <cfRule type="expression" dxfId="15" priority="36">
+      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O262))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="35">
       <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O262))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="36">
-      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O262))</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A276:O276 A281:O282 A277:C280 E277:O280 A284:O284 A283:C283 E283:O283 A286:O287 A285:C285 E285:O285 A290:O290 A288:C289 E288:O289 A294:O294 A291:C293 E291:O293 A295:C295 E295:O295">
-    <cfRule type="expression" dxfId="41" priority="33">
+  <conditionalFormatting sqref="A276:O295">
+    <cfRule type="expression" dxfId="13" priority="5">
       <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O276))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="34">
+    <cfRule type="expression" dxfId="12" priority="6">
       <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O276))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A299:O303">
-    <cfRule type="expression" dxfId="39" priority="29">
+    <cfRule type="expression" dxfId="11" priority="30">
+      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O299))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="29">
       <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O299))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="38" priority="30">
-      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O299))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J26 J920:J922">
-    <cfRule type="expression" dxfId="37" priority="54">
+    <cfRule type="expression" dxfId="9" priority="55">
+      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O25))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="54">
       <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O25))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="36" priority="55">
-      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O25))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J909:J910">
-    <cfRule type="expression" dxfId="35" priority="58">
+    <cfRule type="expression" dxfId="7" priority="59">
+      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O910))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="58">
       <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O910))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="59">
-      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O910))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K341">
-    <cfRule type="expression" dxfId="33" priority="43">
+    <cfRule type="expression" dxfId="5" priority="44">
+      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O341))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="43">
       <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O341))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="44">
-      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O341))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K923:K928">
-    <cfRule type="expression" dxfId="31" priority="41">
+    <cfRule type="expression" dxfId="3" priority="41">
       <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O922))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="42">
+    <cfRule type="expression" dxfId="2" priority="42">
       <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O922))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D277">
-    <cfRule type="expression" dxfId="29" priority="27">
-      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O277))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="28">
-      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O277))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D278">
-    <cfRule type="expression" dxfId="27" priority="25">
-      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O278))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="26" priority="26">
-      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O278))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D279">
-    <cfRule type="expression" dxfId="25" priority="23">
-      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O279))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="24">
-      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O279))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D280">
-    <cfRule type="expression" dxfId="23" priority="21">
-      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O280))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="22">
-      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O280))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D283">
-    <cfRule type="expression" dxfId="21" priority="19">
-      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O283))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="20" priority="20">
-      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O283))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D285">
-    <cfRule type="expression" dxfId="19" priority="17">
-      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O285))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="18">
-      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O285))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D288">
-    <cfRule type="expression" dxfId="17" priority="15">
-      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O288))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="16">
-      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O288))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D289">
-    <cfRule type="expression" dxfId="15" priority="13">
-      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O289))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="14">
-      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O289))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D292">
-    <cfRule type="expression" dxfId="13" priority="11">
-      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O292))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="12">
-      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O292))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D291">
-    <cfRule type="expression" dxfId="11" priority="9">
-      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O291))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="10">
-      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O291))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D293">
-    <cfRule type="expression" dxfId="9" priority="7">
-      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O293))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="8">
-      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O293))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D295">
-    <cfRule type="expression" dxfId="7" priority="5">
-      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O295))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="6">
-      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O295))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D297">
-    <cfRule type="expression" dxfId="5" priority="3">
-      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O297))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="4">
-      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O297))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K297">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O297))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O297))</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>

--- a/data/missing_meta/missing_meta.xlsx
+++ b/data/missing_meta/missing_meta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marco_schuppisser/Desktop/Repository sabseb (new)/metasabseb/data/missing_meta/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{107E5FF8-2E6D-6442-BDD4-FF94BC7BA2B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD88BCB-E5A9-F24B-8B22-8BAAF39F427E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="68640" yWindow="-3860" windowWidth="38400" windowHeight="23500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8242" uniqueCount="2681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8248" uniqueCount="2681">
   <si>
     <t>var_defs_key</t>
   </si>
@@ -8737,41 +8737,11 @@
   <dxfs count="18">
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -8857,6 +8827,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -8877,6 +8857,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -8892,6 +8882,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -11554,6 +11554,9 @@
         <v>1407</v>
       </c>
       <c r="G63" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H63" t="s">
         <v>2207</v>
       </c>
       <c r="I63" t="s">
@@ -11647,6 +11650,9 @@
         <v>1426</v>
       </c>
       <c r="G66" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H66" t="s">
         <v>2207</v>
       </c>
       <c r="I66" t="s">
@@ -12801,6 +12807,9 @@
         <v>1407</v>
       </c>
       <c r="G106" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H106" t="s">
         <v>2207</v>
       </c>
       <c r="I106" t="s">
@@ -12830,6 +12839,9 @@
         <v>1723</v>
       </c>
       <c r="G107" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H107" t="s">
         <v>2207</v>
       </c>
       <c r="I107" t="s">
@@ -30814,6 +30826,9 @@
         <v>2285</v>
       </c>
       <c r="G638" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H638" t="s">
         <v>2207</v>
       </c>
       <c r="I638" t="s">
@@ -30843,6 +30858,9 @@
         <v>2286</v>
       </c>
       <c r="G639" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H639" t="s">
         <v>2207</v>
       </c>
       <c r="I639" t="s">
@@ -34952,67 +34970,67 @@
       <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O297))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:O1 A2:J13 L2:O13 A14:O15 A16:J24 L16:O38 A25:I26 A27:J38 A39:O42 A43:J46 L43:O46 A47:I49 K47:O53 A50:H50 A51:I51 A52:H52 A53:I53 A54:O63 A64:J65 L64:O65 A66:O71 A72:J72 K72:O77 A73:I73 A74:H74 J74 A75:I75 A76:H76 J76 A77:I77 A78:O106 A107:I132 K107:O132 A133:O171 A172:I172 K172:O172 A173:O187 A188:J190 L188:O190 A191:O197 A198:H198 J198:O198 A199:O199 A200:H200 J200:O200 A201:O201 A202:H202 J202:O202 A203:O204 A205:H205 J205:O205 A206:O206 A207:H207 J207:O207 A208:O210 A211:H211 J211:O211 A212:O212 A213:H214 J213:O214 A215:O218 A219:H219 J219:O219 A220:O222 A223:H224 J223:O224 A225:O231 A232:J232 L232:O232 A233:O233 A234:J235 L234:O235 A236:O246 A247:I247 K247:O247 A248:O248 A249:I249 K249:O249 A250:O250 A251:I251 K251:O251 A252:O252 A253:I253 K253:O253 A254:O254 A255:I255 K255:O255 A256:J256 L256:O256 A257:O259 A260:J261 L260:O261 A275:H275 J275:O275 A296:H296 J296 L296:O298 A298:H298 J298 A304:H304 L304:O304 A305:O305 A306:H306 L306:O306 A307:O307 A308:H308 L308:O308 A309:O314 A315:H315 L315:O315 A324:H339 L324:O341 A340:I341 A342:O342 A343:I343 L343:O343 A344:O344 A345:I345 L345:O345 A346:O347 A348:I348 K348:O348 A349:O351 A352:I352 K352:O352 A353:O353 A354:I354 K354:O354 A355:O355 A356:I356 K356:O356 A357:O357 A358:J362 L358:O362 A363:O370 A371:J391 L371:O391 A392:O392 A393:J393 L393:O393 A394:O396 A397:I397 L397:O397 A398:O398 A399:I399 L399:O399 A400:O400 A401:I401 L401:O401 A402:O402 A403:I403 L403:O403 A404:O404 A405:I405 L405:O406 A406:J406 A407:O409 A410:J413 L410:O413 A414:O414 A415:H415 J415 L415:O419 A416:J419 A420:O420 A421:J422 L421:O422 A423:O423 A424:J425 L424:O425 A426:O427 A428:J428 L428:O428 A429:O429 A430:J432 L430:O432 A433:O434 A435:J436 L435:O442 A437:H437 J437 A438:J442 A443:H443 J443:O443 A444:J444 L444:O444 A445:H445 J445:O445 A446:O448 A449:J450 L449:O450 A451:O451 A452:J457 L452:O457 A458:O461 A462:J474 L462:O474 A475:O475 A476:H477 J476:O477 A478:O483 A484:J512 L484:O512 K495 A513:H513 J513:O513 A514:O514 A515:H515 J515:O515 A516:O516 A517:H517 J517:O517 A518:O519 A520:J522 L520:O522 A523:O527 A528:C528 E528:O528 A529:O536 A537:C537 E537:O537 A538:O545 A546:H546 J546:O546 A547:O563 A564:J564 L564:O575 A565:H566 J565:J566 A567:J567 A568:H569 J568:J569 A570:J571 A572:H573 J572:J573 A574:J575 A576:O576 A577:H577 J577 L577:O583 A578:J578 A579:H579 J579 A580:J583 A599:J612 L599:O612 A613:O620 A621:J631 L621:O631 A632:O640 A641:J641 L641:O641 A642:O893 A894:J896 L894:O896 A897:O897 A898:J903 L898:O903 A904:O908 A909:I910 K909:O910 A911:O918 J919 A919:I922 K919:O922 A923:J928 L923:O928 A929:O1048576 A316:O323 A584:O598">
-    <cfRule type="expression" dxfId="1" priority="51">
+  <conditionalFormatting sqref="A1:O1 A2:J13 L2:O13 A14:O15 A16:J24 L16:O38 A25:I26 A27:J38 A39:O42 A43:J46 L43:O46 A47:I49 K47:O53 A50:H50 A51:I51 A52:H52 A53:I53 A64:J65 L64:O65 A72:J72 K72:O77 A73:I73 A74:H74 J74 A75:I75 A76:H76 J76 A77:I77 A78:O105 A108:I132 K107:O132 A133:O171 A172:I172 K172:O172 A173:O187 A188:J190 L188:O190 A191:O197 A198:H198 J198:O198 A199:O199 A200:H200 J200:O200 A201:O201 A202:H202 J202:O202 A203:O204 A205:H205 J205:O205 A206:O206 A207:H207 J207:O207 A208:O210 A211:H211 J211:O211 A212:O212 A213:H214 J213:O214 A215:O218 A219:H219 J219:O219 A220:O222 A223:H224 J223:O224 A225:O231 A232:J232 L232:O232 A233:O233 A234:J235 L234:O235 A236:O246 A247:I247 K247:O247 A248:O248 A249:I249 K249:O249 A250:O250 A251:I251 K251:O251 A252:O252 A253:I253 K253:O253 A254:O254 A255:I255 K255:O255 A256:J256 L256:O256 A257:O259 A260:J261 L260:O261 A275:H275 J275:O275 A296:H296 J296 L296:O298 A298:H298 J298 A304:H304 L304:O304 A305:O305 A306:H306 L306:O306 A307:O307 A308:H308 L308:O308 A309:O314 A315:H315 L315:O315 A316:O323 A324:H339 L324:O341 A340:I341 A342:O342 A343:I343 L343:O343 A344:O344 A345:I345 L345:O345 A346:O347 A348:I348 K348:O348 A349:O351 A352:I352 K352:O352 A353:O353 A354:I354 K354:O354 A355:O355 A356:I356 K356:O356 A357:O357 A358:J362 L358:O362 A363:O370 A371:J391 L371:O391 A392:O392 A393:J393 L393:O393 A394:O396 A397:I397 L397:O397 A398:O398 A399:I399 L399:O399 A400:O400 A401:I401 L401:O401 A402:O402 A403:I403 L403:O403 A404:O404 A405:I405 L405:O406 A406:J406 A407:O409 A410:J413 L410:O413 A414:O414 A415:H415 J415 L415:O419 A416:J419 A420:O420 A421:J422 L421:O422 A423:O423 A424:J425 L424:O425 A426:O427 A428:J428 L428:O428 A429:O429 A430:J432 L430:O432 A433:O434 A435:J436 L435:O442 A437:H437 J437 A438:J442 A443:H443 J443:O443 A444:J444 L444:O444 A445:H445 J445:O445 A446:O448 A449:J450 L449:O450 A451:O451 A452:J457 L452:O457 A458:O461 A462:J474 L462:O474 A475:O475 A476:H477 J476:O477 A478:O483 A484:J512 L484:O512 K495 A513:H513 J513:O513 A514:O514 A515:H515 J515:O515 A516:O516 A517:H517 J517:O517 A518:O519 A520:J522 L520:O522 A523:O527 A528:C528 E528:O528 A529:O536 A537:C537 E537:O537 A538:O545 A546:H546 J546:O546 A547:O563 A564:J564 L564:O575 A565:H566 J565:J566 A567:J567 A568:H569 J568:J569 A570:J571 A572:H573 J572:J573 A574:J575 A576:O576 A577:H577 J577 L577:O583 A578:J578 A579:H579 J579 A580:J583 A584:O598 A599:J612 L599:O612 A613:O620 A621:J631 L621:O631 A632:O637 A641:J641 L641:O641 A642:O893 A894:J896 L894:O896 A897:O897 A898:J903 L898:O903 A904:O908 A909:I910 K909:O910 A911:O918 J919 A919:I922 K919:O922 A923:J928 L923:O928 A929:O1048576 A54:O63 A66:O71 I106:O106 A106:G107 I107 A640:O640 A638:G639 I638:O639">
+    <cfRule type="expression" dxfId="15" priority="50">
+      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O1))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="51">
       <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O1))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="50">
-      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O1))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A262:O274">
-    <cfRule type="expression" dxfId="15" priority="36">
+    <cfRule type="expression" dxfId="13" priority="35">
+      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O262))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="36">
       <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O262))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="35">
-      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O262))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A276:O295">
-    <cfRule type="expression" dxfId="13" priority="5">
+    <cfRule type="expression" dxfId="11" priority="5">
       <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O276))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="6">
+    <cfRule type="expression" dxfId="10" priority="6">
       <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O276))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A299:O303">
-    <cfRule type="expression" dxfId="11" priority="30">
+    <cfRule type="expression" dxfId="9" priority="29">
+      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O299))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="30">
       <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O299))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="29">
-      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O299))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J26 J920:J922">
-    <cfRule type="expression" dxfId="9" priority="55">
+    <cfRule type="expression" dxfId="7" priority="54">
+      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O25))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="55">
       <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O25))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="54">
-      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O25))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J909:J910">
-    <cfRule type="expression" dxfId="7" priority="59">
+    <cfRule type="expression" dxfId="5" priority="58">
+      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O910))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="59">
       <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O910))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="58">
-      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O910))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K341">
-    <cfRule type="expression" dxfId="5" priority="44">
+    <cfRule type="expression" dxfId="3" priority="43">
+      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O341))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="44">
       <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O341))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="43">
-      <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O341))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K923:K928">
-    <cfRule type="expression" dxfId="3" priority="41">
+    <cfRule type="expression" dxfId="1" priority="41">
       <formula>ISNUMBER(SEARCH("Nicht in der Skalendokumentation",$O922))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="42">
+    <cfRule type="expression" dxfId="0" priority="42">
       <formula>ISNUMBER(SEARCH("EMPTY DATA COLUMN",$O922))</formula>
     </cfRule>
   </conditionalFormatting>
